--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0F5D95-A832-4634-912F-DDDD8BA26F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D2BDC9-EBAB-40E0-86F1-DE4999EDC05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
   <sheets>
     <sheet name="usernames" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>username</t>
   </si>
@@ -28,17 +41,59 @@
     <t>display_name</t>
   </si>
   <si>
-    <t>israel_bidur</t>
-  </si>
-  <si>
-    <t>ישראללללל</t>
+    <t>https://www.instagram.com/djyochaiedri/</t>
+  </si>
+  <si>
+    <t>יוחאי אדרי די ג'י</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meni_music/</t>
+  </si>
+  <si>
+    <t>מני ראב די ג'יי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avishairosen/</t>
+  </si>
+  <si>
+    <t>אבישי רוזן זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/musicbylufi/</t>
+  </si>
+  <si>
+    <t>לופי זמר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/elnatansh/</t>
+  </si>
+  <si>
+    <t>אלנתן זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yedidyashpizada/</t>
+  </si>
+  <si>
+    <t>ידידיה שפיזדה חבר של נתן מזרחי</t>
+  </si>
+  <si>
+    <t>לידור יוסף זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lidor___yosef/38SL38DO</t>
+  </si>
+  <si>
+    <t>ערב טוב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/erevtov/3JDJ67SJS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +241,15 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="177"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
@@ -489,7 +553,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -532,11 +596,13 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - הדגשה1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - הדגשה2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - הדגשה3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -562,6 +628,7 @@
     <cellStyle name="הדגשה4" xfId="30" builtinId="41" customBuiltin="1"/>
     <cellStyle name="הדגשה5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="הדגשה6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="היפר-קישור" xfId="42" builtinId="8"/>
     <cellStyle name="הערה" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="חישוב" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="טוב" xfId="6" builtinId="26" customBuiltin="1"/>
@@ -910,8 +977,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314C898-9C37-4B5F-A425-225D45F41FA8}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -922,14 +993,78 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{B2FECCC5-FAF8-407D-8016-358AD744B92A}"/>
+    <hyperlink ref="A8" r:id="rId2" xr:uid="{3633A9EA-DC51-4C90-BA99-8987A2894C2D}"/>
+    <hyperlink ref="A9" r:id="rId3" xr:uid="{EE038DAE-04C8-47BE-8F15-E502A8E36DA6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D2BDC9-EBAB-40E0-86F1-DE4999EDC05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55539867-4284-486B-9271-4CFBFB948BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>username</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>https://www.instagram.com/erevtov/3JDJ67SJS</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noshmim.mizrahit/</t>
+  </si>
+  <si>
+    <t>נושמים</t>
   </si>
 </sst>
 </file>
@@ -1056,6 +1062,14 @@
         <v>16</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
     </row>
@@ -1064,6 +1078,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{B2FECCC5-FAF8-407D-8016-358AD744B92A}"/>
     <hyperlink ref="A8" r:id="rId2" xr:uid="{3633A9EA-DC51-4C90-BA99-8987A2894C2D}"/>
     <hyperlink ref="A9" r:id="rId3" xr:uid="{EE038DAE-04C8-47BE-8F15-E502A8E36DA6}"/>
+    <hyperlink ref="A10" r:id="rId4" xr:uid="{6366DCFC-7E36-4A52-8009-598CDD11E237}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user-01\Downloads\Construction-apps\Construction\Github-Actions-Download-Stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55539867-4284-486B-9271-4CFBFB948BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E899E44-FFC8-4149-9CE9-4C23C2C88BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>username</t>
   </si>
@@ -41,58 +41,10 @@
     <t>display_name</t>
   </si>
   <si>
-    <t>https://www.instagram.com/djyochaiedri/</t>
-  </si>
-  <si>
-    <t>יוחאי אדרי די ג'י</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/meni_music/</t>
-  </si>
-  <si>
-    <t>מני ראב די ג'יי</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/avishairosen/</t>
-  </si>
-  <si>
-    <t>אבישי רוזן זמר</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/musicbylufi/</t>
-  </si>
-  <si>
-    <t>לופי זמר דתי</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/elnatansh/</t>
-  </si>
-  <si>
-    <t>אלנתן זמר</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/yedidyashpizada/</t>
-  </si>
-  <si>
-    <t>ידידיה שפיזדה חבר של נתן מזרחי</t>
-  </si>
-  <si>
-    <t>לידור יוסף זמר</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/lidor___yosef/38SL38DO</t>
-  </si>
-  <si>
     <t>ערב טוב</t>
   </si>
   <si>
     <t>https://www.instagram.com/erevtov/3JDJ67SJS</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/noshmim.mizrahit/</t>
-  </si>
-  <si>
-    <t>נושמים</t>
   </si>
 </sst>
 </file>
@@ -999,75 +951,17 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
+      <c r="A2" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
+      <c r="A8" s="1"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -1075,10 +969,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{B2FECCC5-FAF8-407D-8016-358AD744B92A}"/>
-    <hyperlink ref="A8" r:id="rId2" xr:uid="{3633A9EA-DC51-4C90-BA99-8987A2894C2D}"/>
-    <hyperlink ref="A9" r:id="rId3" xr:uid="{EE038DAE-04C8-47BE-8F15-E502A8E36DA6}"/>
-    <hyperlink ref="A10" r:id="rId4" xr:uid="{6366DCFC-7E36-4A52-8009-598CDD11E237}"/>
+    <hyperlink ref="A9" r:id="rId1" xr:uid="{EE038DAE-04C8-47BE-8F15-E502A8E36DA6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user-01\Downloads\Construction-apps\Construction\Github-Actions-Download-Stories\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E899E44-FFC8-4149-9CE9-4C23C2C88BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A84520F-9F1F-4317-A340-A73D796F8CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>username</t>
   </si>
@@ -45,6 +45,36 @@
   </si>
   <si>
     <t>https://www.instagram.com/erevtov/3JDJ67SJS</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kolbarama/</t>
+  </si>
+  <si>
+    <t>קול ברמה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noshmim.mizrahit/</t>
+  </si>
+  <si>
+    <t>נושמים מזחרית</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/m_laradar/</t>
+  </si>
+  <si>
+    <t>מתחת לרדאר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/glglz/</t>
+  </si>
+  <si>
+    <t>גלגלצ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hazinor/</t>
+  </si>
+  <si>
+    <t>הצינור</t>
   </si>
 </sst>
 </file>
@@ -951,7 +981,44 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>

--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user-01\Downloads\Construction-apps\Construction\Github-Actions-Download-Stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A84520F-9F1F-4317-A340-A73D796F8CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E899E44-FFC8-4149-9CE9-4C23C2C88BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>username</t>
   </si>
@@ -45,36 +45,6 @@
   </si>
   <si>
     <t>https://www.instagram.com/erevtov/3JDJ67SJS</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/kolbarama/</t>
-  </si>
-  <si>
-    <t>קול ברמה</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/noshmim.mizrahit/</t>
-  </si>
-  <si>
-    <t>נושמים מזחרית</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/m_laradar/</t>
-  </si>
-  <si>
-    <t>מתחת לרדאר</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/glglz/</t>
-  </si>
-  <si>
-    <t>גלגלצ</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/hazinor/</t>
-  </si>
-  <si>
-    <t>הצינור</t>
   </si>
 </sst>
 </file>
@@ -981,44 +951,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
+      <c r="A2" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>

--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user-01\Downloads\Construction-apps\Construction\Github-Actions-Download-Stories\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E899E44-FFC8-4149-9CE9-4C23C2C88BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9994F16-F129-49F2-9B8A-B2F60C664A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>username</t>
   </si>
@@ -45,6 +45,42 @@
   </si>
   <si>
     <t>https://www.instagram.com/erevtov/3JDJ67SJS</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kolbarama/</t>
+  </si>
+  <si>
+    <t>קול ברמה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shticktokofficial/</t>
+  </si>
+  <si>
+    <t>שטיקטוק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hidabroottv/?e=c04f86d4-a924-4df5-8ba1-242c88495591&amp;g=5</t>
+  </si>
+  <si>
+    <t>הידברות טיוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dos_celebs_/</t>
+  </si>
+  <si>
+    <t>דוסלבס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mizrahitpage/</t>
+  </si>
+  <si>
+    <t>מזרחית</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/glglz/</t>
+  </si>
+  <si>
+    <t>גלגלצ</t>
   </si>
 </sst>
 </file>
@@ -951,7 +987,52 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>

--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user-01\Downloads\Construction-apps\Construction\Github-Actions-Download-Stories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9994F16-F129-49F2-9B8A-B2F60C664A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E899E44-FFC8-4149-9CE9-4C23C2C88BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>username</t>
   </si>
@@ -45,42 +45,6 @@
   </si>
   <si>
     <t>https://www.instagram.com/erevtov/3JDJ67SJS</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/kolbarama/</t>
-  </si>
-  <si>
-    <t>קול ברמה</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/shticktokofficial/</t>
-  </si>
-  <si>
-    <t>שטיקטוק</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/hidabroottv/?e=c04f86d4-a924-4df5-8ba1-242c88495591&amp;g=5</t>
-  </si>
-  <si>
-    <t>הידברות טיוי</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/dos_celebs_/</t>
-  </si>
-  <si>
-    <t>דוסלבס</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/mizrahitpage/</t>
-  </si>
-  <si>
-    <t>מזרחית</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/glglz/</t>
-  </si>
-  <si>
-    <t>גלגלצ</t>
   </si>
 </sst>
 </file>
@@ -987,52 +951,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A2" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>

--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user-01\Downloads\01 ניתן למחוק\יוזרים אינסטגרם להורדה אוטומטית\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9994F16-F129-49F2-9B8A-B2F60C664A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DF8BFF-6A45-4DC0-846B-AC1CA42DE795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="956">
   <si>
     <t>username</t>
   </si>
@@ -41,46 +41,2866 @@
     <t>display_name</t>
   </si>
   <si>
+    <t>https://www.instagram.com/djyochaiedri/</t>
+  </si>
+  <si>
+    <t>יוחאי אדרי די ג'י</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meni_music/</t>
+  </si>
+  <si>
+    <t>מני ראב די ג'יי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avishairosen/</t>
+  </si>
+  <si>
+    <t>אבישי רוזן זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/musicbylufi/</t>
+  </si>
+  <si>
+    <t>לופי זמר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/elnatansh/</t>
+  </si>
+  <si>
+    <t>אלנתן זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yedidyashpizada/</t>
+  </si>
+  <si>
+    <t>ידידיה שפיזדה חבר של נתן מזרחי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lidor___yosef/</t>
+  </si>
+  <si>
+    <t>לידור יוסף זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shilo_elia_/</t>
+  </si>
+  <si>
+    <t>שילה אליה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hen_neeman_grayman/</t>
+  </si>
+  <si>
+    <t>חן גריימן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/akiva.official/</t>
+  </si>
+  <si>
+    <t>עקיבא</t>
+  </si>
+  <si>
+    <t>http://www.instagram.com/shirdavidgadasi/</t>
+  </si>
+  <si>
+    <t>שיר דוד גדסי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idan_wilkis/</t>
+  </si>
+  <si>
+    <t>עידן ווילקיס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_natan_mizrachi_/</t>
+  </si>
+  <si>
+    <t>נתן מזרחי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yossef_picasso/</t>
+  </si>
+  <si>
+    <t>יוסף פיקאסו ראפר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_amitmaimon/</t>
+  </si>
+  <si>
+    <t>עמית מימון חבר של נתן מזרחי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shlomo__abraham/</t>
+  </si>
+  <si>
+    <t>שלמה אברהם זמר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nitay_buskila/</t>
+  </si>
+  <si>
+    <t>‎ניתאי בוסקילה נער זמר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itaydavidofficial/</t>
+  </si>
+  <si>
+    <t>איתי דוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haimisraelofficial/</t>
+  </si>
+  <si>
+    <t>חיים ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chaim_zippel_/</t>
+  </si>
+  <si>
+    <t>חיים ציפל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yair_elitzur_official/</t>
+  </si>
+  <si>
+    <t>יאיר אלייצור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yossefbuskila/</t>
+  </si>
+  <si>
+    <t>יוסף חיים בוסקילה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yosefhaimzohar/</t>
+  </si>
+  <si>
+    <t>יוסף חיים זוהר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nussiliberman/</t>
+  </si>
+  <si>
+    <t>נותי ליברמן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/netanelisrael_official/</t>
+  </si>
+  <si>
+    <t>נתנאל ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/srulibroncher/</t>
+  </si>
+  <si>
+    <t>שרולי ברונכר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/qmitsharabi/</t>
+  </si>
+  <si>
+    <t>עמית שרעבי - זמר ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hen_biton44/</t>
+  </si>
+  <si>
+    <t>חן ביטון - ילד זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shay_ben_aroya/</t>
+  </si>
+  <si>
+    <t>שי בן ארויה - זמר ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hananbenariofficial/</t>
+  </si>
+  <si>
+    <t>חנן בן ארי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/inon_eliya/</t>
+  </si>
+  <si>
+    <t>ינון אליה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ilay_avidani/</t>
+  </si>
+  <si>
+    <t>עילי אבידני</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ballagan_sessions/</t>
+  </si>
+  <si>
+    <t>בלגן סשן ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rizika_rap/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏רז נוחיאן‏ ראפר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lee_ovadia/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏לי עובדיה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gilosssssss/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎גיל בנדרלי ראפר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yossef_blueman/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יוסף בלומן זמר דתלש </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eyal_levi_official/</t>
+  </si>
+  <si>
+    <t>אייל לוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liam__golan/</t>
+  </si>
+  <si>
+    <t>ליאם גולן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benaia_barabi/</t>
+  </si>
+  <si>
+    <t>בניה ברבי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/boi_vibe_ish_/</t>
+  </si>
+  <si>
+    <t>וייב איש</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maorelu/</t>
+  </si>
+  <si>
+    <t>מאור ארגוב ראפר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maorashkenazi_/</t>
+  </si>
+  <si>
+    <t>מאור אשכנזי ראפר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dan_avivi_music/</t>
+  </si>
+  <si>
+    <t>דן חביבי חבר של נתן מזרחי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moshe._ohayon/</t>
+  </si>
+  <si>
+    <t>משה אוחיון בחור ראפר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chen_porati/</t>
+  </si>
+  <si>
+    <t>חן פורתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ariel._.azulay1/</t>
+  </si>
+  <si>
+    <t>אריאל אזולאי נער זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/adir__yakov/</t>
+  </si>
+  <si>
+    <t>אדיר יעקב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/balishag__/</t>
+  </si>
+  <si>
+    <t>באלישג - ראפר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tzukush/</t>
+  </si>
+  <si>
+    <t>צוקוש</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omeradam/</t>
+  </si>
+  <si>
+    <t>עומר אדם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/duda_gang_official/</t>
+  </si>
+  <si>
+    <t>דודא גאנג</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yageloshri1/</t>
+  </si>
+  <si>
+    <t>יגל אושרי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itaylevi7/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yamrefaeli/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/oshercohen/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ilay_elmakys/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal__adam/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yonathan_hertz/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yuval_duda/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/odeyaazoulay/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/boi_vibe_ish_/?hl=en</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_orisaban/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ronhayunofficial/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ravid_plotnik/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liornarkis/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/officialeliad/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yonatankalimi/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maoredriofficial/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nathangoshen/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/static/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/stephane.le.gar/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/edennhason/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idob.official/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shahartavoch/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shreki/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shaharsaul/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sasson_ifram_shaulov/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eyalgolan1/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kfirtsafrir/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nadav_hanzis/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/peled__/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idomalka29/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bartzabary/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ben.zur/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎איתי לוי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ים רפאלי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אושר כהן‏ </t>
+  </si>
+  <si>
+    <t>עילאי אלמקייס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎גל אדם </t>
+  </si>
+  <si>
+    <t>יונתן הרץ זמר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דודא‏ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אודיה אזולאי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">וייב איש זמר </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏️אורי סבאן‏ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏רון חיון‏ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">רביד פלוטניק‏ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">בניה ברבי‏ </t>
+  </si>
+  <si>
+    <t>ליאור נרקיס</t>
+  </si>
+  <si>
+    <t>אליעד</t>
+  </si>
+  <si>
+    <t>יונתן קלימי</t>
+  </si>
+  <si>
+    <t>מאור אדרי</t>
+  </si>
+  <si>
+    <t>נתן גושן</t>
+  </si>
+  <si>
+    <t>סטטיק</t>
+  </si>
+  <si>
+    <t>סטפן לגר</t>
+  </si>
+  <si>
+    <t>עדן חסון</t>
+  </si>
+  <si>
+    <t>עידו בי</t>
+  </si>
+  <si>
+    <t>שחר טבוך</t>
+  </si>
+  <si>
+    <t>שרק ראפר</t>
+  </si>
+  <si>
+    <t>שחר סאול</t>
+  </si>
+  <si>
+    <t>ששון שאולוב</t>
+  </si>
+  <si>
+    <t>אייל גולן</t>
+  </si>
+  <si>
+    <t>כפיר צפריר</t>
+  </si>
+  <si>
+    <t>יובל דודה</t>
+  </si>
+  <si>
+    <t>נדב חנציס</t>
+  </si>
+  <si>
+    <t>פלד ראפר</t>
+  </si>
+  <si>
+    <t>עידו מלכה</t>
+  </si>
+  <si>
+    <t>בר צברי</t>
+  </si>
+  <si>
+    <t>בן צור</t>
+  </si>
+  <si>
+    <t>אהבת השם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/or_korem/</t>
+  </si>
+  <si>
+    <t>אור קורם חבר של דילן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idantelem_/</t>
+  </si>
+  <si>
+    <t>אינדה גיים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benkeysar/</t>
+  </si>
+  <si>
+    <t>בן קיסר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rontroyan/</t>
+  </si>
+  <si>
+    <t>רון טרויאן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shaiyomtov/</t>
+  </si>
+  <si>
+    <t>שי יום טוב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/erez_kalderon/</t>
+  </si>
+  <si>
+    <t>ארז קלדרון חטוף</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/grincess_lera/</t>
+  </si>
+  <si>
+    <t>לרה גרינסס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/guy_eitan/</t>
+  </si>
+  <si>
+    <t>גיא איתן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zehavioz/</t>
+  </si>
+  <si>
+    <t>עוז זהבי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benyaminburyevmusic/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בנימין בורייב מחקה את עדן בן זקן  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yagil_yaakov/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יגיל יעקב חטוף </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/or_yaakov18/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אור יעקו‏ב חטוף  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hapshutaofficial/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הפשוטע‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yotzim/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יותם זמרי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bariysirtonim/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הסרטונים של ברי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/malahi1217/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎מלאכי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal_bargig/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גל בַרגִיג מעריצה של עדן חסון‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liron_ofir/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎לירון אופיר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jonathan_grosman1/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יהונתן גרוסמן‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itzikreuven10/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎איציק ראובן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omri_hayoon/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏עומרי חיון‏ רכילות </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maxbhman/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מקס בחמן גומי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eladrabi12/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ספר בטיקטוק </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yotam_gavriel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יותם גבריאל חבר של עדן חסון </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yali__moscovith/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">צייר יהלי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eranswis/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ערן סוויסה רכילות  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rahums/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎רחום יוטיובר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nicole_edlind/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ניקול אדלינד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/agamnava1234/?g=5</t>
+  </si>
+  <si>
+    <t>‏גברת שווארמה🐄</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/michael_yosefyan/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מיכאל יוספיאן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/matan_skaytel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מתן סקייטל יוצר דיגיטלי תימני עממי| </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dylendror/</t>
+  </si>
+  <si>
+    <t>דילן דרור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/alex_shults/</t>
+  </si>
+  <si>
+    <t>אלכס שולץ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yonaeshet/</t>
+  </si>
+  <si>
+    <t>יונה אשד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idanshalva/</t>
+  </si>
+  <si>
+    <t>עידן שלוה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yhonatan.shtivi/</t>
+  </si>
+  <si>
+    <t>יונתן שתיוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moshe_korsia/</t>
+  </si>
+  <si>
+    <t>משה כורסיה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nessi_tikshoret_tveria/</t>
+  </si>
+  <si>
+    <t>נסי תקשורת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/galgul_halaly/</t>
+  </si>
+  <si>
+    <t>גלגול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shuki_salomon/</t>
+  </si>
+  <si>
+    <t>שוקי סלומון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/orlasryofficial/</t>
+  </si>
+  <si>
+    <t>אור לסרי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mreviatar/</t>
+  </si>
+  <si>
+    <t>אביתר עוזרי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/alfiguri/</t>
+  </si>
+  <si>
+    <t>גורי אלפי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yankigoldhaber/</t>
+  </si>
+  <si>
+    <t>יענקי גולדהבר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yahli_watson/</t>
+  </si>
+  <si>
+    <t>יהלי ווטסון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yali__gabay</t>
+  </si>
+  <si>
+    <t>יהלי גבאי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liorsuchard/</t>
+  </si>
+  <si>
+    <t>ליאור סושרד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/assiazar/</t>
+  </si>
+  <si>
+    <t>אסי עזר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kobi_drive/</t>
+  </si>
+  <si>
+    <t>קובי כהן מורה נהיגה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/oranatedgi/</t>
+  </si>
+  <si>
+    <t>אורן אטדגי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jonny_hishgozim/</t>
+  </si>
+  <si>
+    <t>ג'וני חישגוזים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/d.pro__/</t>
+  </si>
+  <si>
+    <t>די פרו בונה משאית</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/elad__turgeman/</t>
+  </si>
+  <si>
+    <t>אליעד תורגמן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noya_ashash1/</t>
+  </si>
+  <si>
+    <t>נויה אשש חברה של אייל לוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nadir_eliyahou/</t>
+  </si>
+  <si>
+    <t>נדיר אליהו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/barjeell/?e=884a101e-9b8f-4240-afd7-17196003558e&amp;g=5</t>
+  </si>
+  <si>
+    <t>ברגיל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idan.keret/reels/</t>
+  </si>
+  <si>
+    <t>עידן קרט</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/donev1_/reels/</t>
+  </si>
+  <si>
+    <t>דונב בחור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/edrikobi/?e=a288bb65-06fc-4b56-a7e1-4e3b07fd1753&amp;g=5</t>
+  </si>
+  <si>
+    <t>קובי אדרי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal_zinger/</t>
+  </si>
+  <si>
+    <t>גל זינגר גלשן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yosef.haim10/</t>
+  </si>
+  <si>
+    <t>יוסף חיים סבג בלוגר ננח</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omerkoly/?e=b785a882-b2c7-4ade-ac28-fcfc57ede7e2&amp;g=5</t>
+  </si>
+  <si>
+    <t>עומר קולי מגיב על סרטונים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noam.takla7/</t>
+  </si>
+  <si>
+    <t>נועם טקלה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yali_tattoo/</t>
+  </si>
+  <si>
+    <t>יהלי צייר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tal_shenhav/</t>
+  </si>
+  <si>
+    <t>טל שנהב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omer.yaron/</t>
+  </si>
+  <si>
+    <t>עומר ירון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noamhimself/</t>
+  </si>
+  <si>
+    <t>נועם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/amitsegalnews/</t>
+  </si>
+  <si>
+    <t>עמית סגל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ron.kav/</t>
+  </si>
+  <si>
+    <t>רון קבונסקי</t>
+  </si>
+  <si>
+    <t>עומר הוריון עמוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakirbarzohar/</t>
+  </si>
+  <si>
+    <t>‎יקיר בר זוהר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/giladby__/</t>
+  </si>
+  <si>
+    <t>גיל נער חמוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shonmizrachi/</t>
+  </si>
+  <si>
+    <t>שון מזרחי‎ סטנדאפיסט</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sabantwins_/</t>
+  </si>
+  <si>
+    <t>תאומים מפורסמים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omri.malinsky02/</t>
+  </si>
+  <si>
+    <t>עומרי מלינסקי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omrilevi9/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עומרי לוי‎ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gilelimelech/</t>
+  </si>
+  <si>
+    <t>גיל אלימלך</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rotem_asherov/</t>
+  </si>
+  <si>
+    <t>רותם אשרוב יוטיובר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/isaac.lasry/</t>
+  </si>
+  <si>
+    <t>יצחק לסרי דתי יוטיובר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yonitovim/</t>
+  </si>
+  <si>
+    <t>יוני טובים הומו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yarin_hamevin/</t>
+  </si>
+  <si>
+    <t>ירין מבין</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ohad.avitbul/</t>
+  </si>
+  <si>
+    <t>אוהד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liat_berkovich_kraviz/</t>
+  </si>
+  <si>
+    <t>‎ליאת ברקוביץ קרביץ על שם יקיר בר זוהר סבי ומורי‎ (@liat_berkovich_kraviz) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nirbenilush10/</t>
+  </si>
+  <si>
+    <t>‎ניר בנילוש‎ (@nirbenilush10) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nitay_yona_news/</t>
+  </si>
+  <si>
+    <t>‎הכתב הצעיר - נתאי יונה 📢‎ (@nitay_yona_news) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mrshibolet/</t>
+  </si>
+  <si>
+    <t>מר שיבולת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sniravitan23/</t>
+  </si>
+  <si>
+    <t>‎שניר אביטן‎ (@sniravitan23) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/i_am_the_shadow/</t>
+  </si>
+  <si>
+    <t>הצל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ahavat_goldenboy/?e=1f142175-db05-406d-a147-cbb2e277a09d&amp;g=5</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avia_productions/</t>
+  </si>
+  <si>
+    <t>אביה הפקות מנהל של אלייצור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/or_cohen_keyboard/</t>
+  </si>
+  <si>
+    <t>אור כהן חבר של עדן חסון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avihay.idan/</t>
+  </si>
+  <si>
+    <t>אניווי עידן מנגן על קנון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/assafcohen15/</t>
+  </si>
+  <si>
+    <t>אסף כהן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_kubani/</t>
+  </si>
+  <si>
+    <t>בר הפקות מוזיקאי חבר של יוסף בוסקילה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/guykumusic/</t>
+  </si>
+  <si>
+    <t>גיקו מיוזיק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/david_avraham_carmi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דוד כרמי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/davids__band/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דוד שם טוב‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zeev6356326/</t>
+  </si>
+  <si>
+    <t>זאבי רבינוביץ חבר של שרולי ברונכר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zivnoyman/?e=c8308a4b-88e0-4732-8282-94fcb1eae831&amp;g=5</t>
+  </si>
+  <si>
+    <t>‎זיו נוימן‎ מנגן על קנון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haimshaked_productions/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חיים שקד מפיק של איתי דוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/talforer/</t>
+  </si>
+  <si>
+    <t>טל פורר מפיק אלייצור ועוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakovzeyakov/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יעקב אסרף גיטריסט של ריבו ועוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakir_hiyaev_music/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יקיר חייאב </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yarin_yacobi/</t>
+  </si>
+  <si>
+    <t>ירין יעקובי מנהל אולפן של שרק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel_elgrabli/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ישראל אלגרבלי | כותב שירים✏️‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mccohen/</t>
+  </si>
+  <si>
+    <t>כהן מפיק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/leibalelipsker/</t>
+  </si>
+  <si>
+    <t>לייבלה ליפסקר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/doronsery/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎מפיק לזמרים דורון סרי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israelr2/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מפיק של זמרים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moshe.dotan/</t>
+  </si>
+  <si>
+    <t>משה דותן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nuta.levin/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נוטע לוין מפיק חסידי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noam_akrabi/</t>
+  </si>
+  <si>
+    <t>נועם עקרבי מוזיקאי טכני</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yarinalushstudio/</t>
+  </si>
+  <si>
+    <t>סטודיו ירין אלוש עטיפות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/adiel__cohen/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎עדיאל כהן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/oz_altman/?e=72f92188-1183-4693-8895-1e00e8224989&amp;g=5</t>
+  </si>
+  <si>
+    <t>עוז אלטמן דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/offernissimofficial/?e=cc37f1b4-dc98-4514-86a2-20b783b96383&amp;g=5</t>
+  </si>
+  <si>
+    <t>עופר ניסים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/amit.bracha/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎עמית ברכה זמר ומוזיקאי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_ranicohen/</t>
+  </si>
+  <si>
+    <t>רוני כהן להקת ניגון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sikurim_israel/</t>
+  </si>
+  <si>
+    <t>חדש בעגלה - מוצרים חדשים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mobile1_music/</t>
+  </si>
+  <si>
+    <t>מובייל מיוזיק - חברת מוזיקה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kaspit_art/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כספית ייצוג אמנים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yomi_news/</t>
+  </si>
+  <si>
+    <t>יומי ניוז</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/theking.dylen16/</t>
+  </si>
+  <si>
+    <t>עמוד הערכה לדילן המושלם❤️❤️</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kolbarama/</t>
+  </si>
+  <si>
+    <t>קול ברמה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shticktokofficial/</t>
+  </si>
+  <si>
+    <t>שטיקטוק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nihnaslketzev/?e=7c54d91e-c509-450d-b7dc-e3f41743ee1c&amp;g=5</t>
+  </si>
+  <si>
+    <t>נכנס לקצב - מסיבות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kan_israel/</t>
+  </si>
+  <si>
+    <t>כאן ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hidabroottv/?e=c04f86d4-a924-4df5-8ba1-242c88495591&amp;g=5</t>
+  </si>
+  <si>
+    <t>הידברות טיוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hizukim24/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏חיזוקים_24_‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kuparashit1/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏קופה ראשית‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noshmim.mizrahit/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏נושמים מזרחית‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/flash_news_il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏חדשות פלאש </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hacelebs_shel_hachibur/</t>
+  </si>
+  <si>
+    <t>הסלבס של הציבור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israelissm/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ישראליזם‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/farmax_amisraelhi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎עם ישראל חי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idfonline/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏צהל - צבא ההגנה לישראל‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dos_celebs_/</t>
+  </si>
+  <si>
+    <t>‏דוס סלבס העמוד הרשמי❗</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dos_celebs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דוסלבס סטטוס‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dos_celebs_status/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israeli_songs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏שירים ישראלים העמוד הרשמי🇮🇱‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dati_bidur/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דתי בידור 🌟העמוד הרשמי🌟‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mizrahitpage/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מזרחית באינסטגרם‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/24tv/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ערוץ 24‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/i24news_he/</t>
+  </si>
+  <si>
+    <t>24 ניוז</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lsrael.music/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ישראל מיוזיק‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/big.tora.il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏בּוֹרֵא עוֹלָם תּוֹדָה </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hotbiduronline/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הוט בידור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itmodels/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎סוכנות דוגמנות </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/humor_asor.il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הומור אסור ישראל </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yomsheniofficial/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יום שני </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/justmusic.college/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מכללת ג׳אסט מיוזיק‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel.business/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ישראל ביזנס‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/newsaskan/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏חדשות עסקן‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ronybidortiktok/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏רוני בידור טיקטוק‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tzama_music/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏צמאה | לחיות את הניגון🎶‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rj_veronika7/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אמנות נייר חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/messudarot/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מסודרות | אריזה ופריקה במעבר דירה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ahuz.ehad/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אחוז אחד‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hapitgam/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הפתגם היומי🤍‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/todaxco/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏תודה חולצות </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/apargod_chadashot/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏חדשות הפרגוד‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/apr_god/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הפרגוד‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/olam_il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מסביב לעולם 🌍 יהונתן ואריאל‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/funny.is.healthy/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מצחיק זה בריא🤣‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_electro_beats/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אלקטרו ביטס </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yam_ahzakot/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ים אחזקות | ניהול מבנים | אחזקה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/link__il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏לינק ישראל‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/radiokolyezreel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏רדיו קול יזרעאל | ניו מדיה באקדמיה </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hakufsah/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הקופסה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kirkushim.tb/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏קירקושים אמנות על קירות‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gadgetlandil/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עולם של גאדג׳טים✨‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/microsoft_rnd_israel/</t>
+  </si>
+  <si>
+    <t>מיקרוסופט ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/today_and_before/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">היום ולפני📆‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/insane_kosherkravi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אינסיין כושר קרבי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pumpi_il/</t>
+  </si>
+  <si>
+    <t>פאמפי‏ פאמפי הדלקן שחוסך ליטרים של זמן וכסף</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/signon_corp/</t>
+  </si>
+  <si>
+    <t>סגנון עמוד ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nishmat_kol_hai_djs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏נשמת קול חי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/johny.turbo/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כל מה שקשור לעולם המוטורי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/995fm/</t>
+  </si>
+  <si>
+    <t>🔥רדיו 99.5 חם-אש🔥</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/standupfactory/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏סטנדאפ פקטורי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fixfixfixfix/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חברת בגדים מיניונים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/barangay__/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ברנז׳ה‏ חרדי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hizukim_yomii/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חיזוקים לזיכוי הרבים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kanmoreshet/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏כאן מורשת‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/joymobile.co.il/</t>
+  </si>
+  <si>
+    <t>חנות טלפונים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eranchen_photographer/</t>
+  </si>
+  <si>
+    <t>ארן חן | צלמים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/abamevich/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אבא מביך‏ </t>
+  </si>
+  <si>
+    <t>http://instagram.com/scopt/</t>
+  </si>
+  <si>
+    <t>חדשות סקופט</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/harabanit/</t>
+  </si>
+  <si>
+    <t>הרבנית</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shmua_bidur/</t>
+  </si>
+  <si>
+    <t>שמועה בידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/datiim_bareshet/</t>
+  </si>
+  <si>
+    <t>דתיים ברשת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/frogifrogi/</t>
+  </si>
+  <si>
+    <t>פרוגי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel_bidur/</t>
+  </si>
+  <si>
+    <t>ישראל בידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/erevtov/</t>
+  </si>
+  <si>
     <t>ערב טוב</t>
   </si>
   <si>
-    <t>https://www.instagram.com/erevtov/3JDJ67SJS</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/kolbarama/</t>
-  </si>
-  <si>
-    <t>קול ברמה</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/shticktokofficial/</t>
-  </si>
-  <si>
-    <t>שטיקטוק</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/hidabroottv/?e=c04f86d4-a924-4df5-8ba1-242c88495591&amp;g=5</t>
-  </si>
-  <si>
-    <t>הידברות טיוי</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/dos_celebs_/</t>
-  </si>
-  <si>
-    <t>דוסלבס</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/mizrahitpage/</t>
-  </si>
-  <si>
-    <t>מזרחית</t>
+    <t>https://www.instagram.com/wallanews/</t>
+  </si>
+  <si>
+    <t>וואלה ניוז</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/wallacelebs/</t>
+  </si>
+  <si>
+    <t>וואלה סלבס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/m_laradar/</t>
+  </si>
+  <si>
+    <t>מתחת לרדאר</t>
+  </si>
+  <si>
+    <t>עומרי חיון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/wallaentertainment/</t>
+  </si>
+  <si>
+    <t>וואלה תרבות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/news.bidur</t>
+  </si>
+  <si>
+    <t>חדשות הבידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hambamedia/</t>
+  </si>
+  <si>
+    <t>חם במדיה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/makocelebs/</t>
+  </si>
+  <si>
+    <t>מאקו סלבס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kan_gimel/</t>
+  </si>
+  <si>
+    <t>כאן גימל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kan_reshetb/</t>
+  </si>
+  <si>
+    <t>כאן רשת ב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kikarhashabat/</t>
+  </si>
+  <si>
+    <t>כיכר השבת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/live_bidur/</t>
+  </si>
+  <si>
+    <t>לייב בידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/artcoeur_israel/</t>
+  </si>
+  <si>
+    <t>ארטקור הפקות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lionmotivationil/</t>
+  </si>
+  <si>
+    <t>משפטים מועדון האריות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/storyill/</t>
+  </si>
+  <si>
+    <t>סטוריל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bardak613/</t>
+  </si>
+  <si>
+    <t>ברדק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shticktokofficial1/</t>
+  </si>
+  <si>
+    <t>שטיקטוק גיבוי</t>
   </si>
   <si>
     <t>https://www.instagram.com/glglz/</t>
   </si>
   <si>
     <t>גלגלצ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yomtov_tonight/</t>
+  </si>
+  <si>
+    <t>יומטוב טו נייט</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/radar_il/</t>
+  </si>
+  <si>
+    <t>ראדר אי אל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/cattleya_eyewear/</t>
+  </si>
+  <si>
+    <t>קאטלייה טרנדים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/celebs.notifications/</t>
+  </si>
+  <si>
+    <t>עדכוני סלבס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/push.il/</t>
+  </si>
+  <si>
+    <t>פוש חדשות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pnaiplus/</t>
+  </si>
+  <si>
+    <t>פנאי פלוס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/musiclitonfire_1/</t>
+  </si>
+  <si>
+    <t>סרטוני מוזיקה דתיים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/icon_israel_/</t>
+  </si>
+  <si>
+    <t>אייקון ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/besties.israel/</t>
+  </si>
+  <si>
+    <t>בסטיז בידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bafront.pr</t>
+  </si>
+  <si>
+    <t>בפרונט דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yagil.yaakov.fans/</t>
+  </si>
+  <si>
+    <t>עמוד ליגיל יעקב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel_bidur_gaming/</t>
+  </si>
+  <si>
+    <t>ישראל בידור גיימינג</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israella.music/</t>
+  </si>
+  <si>
+    <t>ישראלה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/booqueen.il/</t>
+  </si>
+  <si>
+    <t>בוקיואין מנהלי הפקות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/newsfash/</t>
+  </si>
+  <si>
+    <t>חדשות האופנה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_u.smile_/</t>
+  </si>
+  <si>
+    <t>חיל חיוך</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hazinor/</t>
+  </si>
+  <si>
+    <t>הצינור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tiktokshow_il/</t>
+  </si>
+  <si>
+    <t>טיקטוק שואו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maarivonline/</t>
+  </si>
+  <si>
+    <t>מעריב אונליין</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/keshet12/</t>
+  </si>
+  <si>
+    <t>קשת 12</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ildailymotivation/</t>
+  </si>
+  <si>
+    <t>מוטיבציה יומיומית</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/the_next_step_il/</t>
+  </si>
+  <si>
+    <t>הצעד הבא מוטיבציה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omer_adam_my_life_/</t>
+  </si>
+  <si>
+    <t>עומר אדם מיי לייף עמוד לעומר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sta2sim_metzaitzim</t>
+  </si>
+  <si>
+    <t>סטטוסים מצייצים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/arutz.sheva/reels/</t>
+  </si>
+  <si>
+    <t>ערוץ שבע</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/funny.li.1/reels/</t>
+  </si>
+  <si>
+    <t>לצחוק זה בריא</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hiphopisrael/</t>
+  </si>
+  <si>
+    <t>היפהופ ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/amit.hashai/</t>
+  </si>
+  <si>
+    <t>בחשאי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/audioter_il/</t>
+  </si>
+  <si>
+    <t>אודיותר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/newsil.ontime/</t>
+  </si>
+  <si>
+    <t>חדשות בזמן אמת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/news.0nline/</t>
+  </si>
+  <si>
+    <t>ניוז אונליין</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/halal.il/</t>
+  </si>
+  <si>
+    <t>מסע בחלל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hustle_hub.il/</t>
+  </si>
+  <si>
+    <t>עמוד שמראיין עשירים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lsrael_office/</t>
+  </si>
+  <si>
+    <t>ישראל בידור אופיס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jewish_battle/</t>
+  </si>
+  <si>
+    <t>בטל ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hadmor.il/</t>
+  </si>
+  <si>
+    <t>‎האדמור‎ (@hadmor.il) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rehovtoomtoom/</t>
+  </si>
+  <si>
+    <t>רחוב טומטום</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dorian_parkour/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ספורטאי חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/marssiek/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎צלם חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/marssiek/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎צלם הולנדי חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/thekiryalife/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎קיריה קולסניקוב עושה מתיחות ברחוב חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ai.boysphotograph/</t>
+  </si>
+  <si>
+    <t>‏‎עמוד תמונות גלריית בנים בינה מלאכותית   חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/realadamrose/</t>
+  </si>
+  <si>
+    <t>כוכב בידור חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/troyesivan/</t>
+  </si>
+  <si>
+    <t>טרוי סיוון זמר יהודי אוסטרלי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/learnwithvalerio/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎מדע וטכנולוגיה חול   </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zachchoi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎טבח חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sergio_outdoors/</t>
+  </si>
+  <si>
+    <t>‏‎פטנטים  חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idealizandocoisas/</t>
+  </si>
+  <si>
+    <t>‏‎‏‎תיקונים ופטנטים חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/quick_fix_life_4727/</t>
+  </si>
+  <si>
+    <t>‏‎תיקונים ופטנטים  חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/daniellabelle1/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎סרטונים מגניבים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/loopedlaces/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קשירת שרוכים חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/laivy.miller/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎זמרים יהודים אמריקאים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/abdul_sistem/</t>
+  </si>
+  <si>
+    <t>‏‎טריקים מחשבים  חול</t>
+  </si>
+  <si>
+    <t>עושה קפיצות ועוד חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/parkour_athlete_/</t>
+  </si>
+  <si>
+    <t>חול פרקור ספורטאי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/axelydaniel/</t>
+  </si>
+  <si>
+    <t>אלכס ודניאל זוג חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yuki_nara77/</t>
+  </si>
+  <si>
+    <t>בנות הלבשה תחתונה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/brave.gals/reels/</t>
+  </si>
+  <si>
+    <t>יוצרת תוכן חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gabrielsilva1k/reels/</t>
+  </si>
+  <si>
+    <t>גבריאל סילבה קומיקאי ויוצר  תוכן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tatebutts/?e=fe7174fa-c38e-407e-8ebb-cfc510f91c35&amp;g=5</t>
+  </si>
+  <si>
+    <t>זמר ילד חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/konraddamer/</t>
+  </si>
+  <si>
+    <t>נער חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/or_efraim/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אור אפרים שיווק </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ariel.kigel.social.media/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אריאל קיגל </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/virtualmedia.il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">וירטואל מדיה שיווק </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idoshafirr/</t>
+  </si>
+  <si>
+    <t>עידו שפיר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ofek_hilali/</t>
+  </si>
+  <si>
+    <t>אופק הללי עורך וידאו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/illy_alfia/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אִילִּי אלפיה צלם וולוגר‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eli_sadeh_videoagapher/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אלי שדה צילום וידאו‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yehonatan5/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎גוני צלם ועורך וידאו </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal_isaev/#</t>
+  </si>
+  <si>
+    <t>גל איסייב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal_isaev2/#</t>
+  </si>
+  <si>
+    <t>גל איסייב עמוד שני</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/davidgold.video/</t>
+  </si>
+  <si>
+    <t>דוד גולדשטיין צלם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/___yakirphoto1___/</t>
+  </si>
+  <si>
+    <t>יקיר דהאן צלם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/isaac_kelman_/</t>
+  </si>
+  <si>
+    <t>ישראל קלמן צלם חבר של שרולי ברונכר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maor_kesem_livshiz/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מאור קסם ליבשיץ | גרפיקאי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meni_3030/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מנחם שאער | צלם סטילס </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/matanmalahovski/</t>
+  </si>
+  <si>
+    <t>מתן מליכובסקי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noamtryber/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏נועם טרייבר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nirahiel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ניר אחיאל | מעצב גרפי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/the_giant01/</t>
+  </si>
+  <si>
+    <t>נתי תורגמן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/phoenixmedia.official/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פניקס מדיה מפורסמים‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shimi__photos/</t>
+  </si>
+  <si>
+    <t>שימי פוטוס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shneor_shif/</t>
+  </si>
+  <si>
+    <t>שניאור שיף</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/aviya.rosenheim/</t>
+  </si>
+  <si>
+    <t>אבייה רוזנהיים סאס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/alon_gefen/</t>
+  </si>
+  <si>
+    <t>אלון גפן אוטומציה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/daniel.moldawsky/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎דניאל מולידבסקי דרופשיפינג </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kristalmediia/</t>
+  </si>
+  <si>
+    <t>דניאל קריסטל נער יזם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/talecomlaunch/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎טל רוטר איקומרס </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/naorhacmon/</t>
+  </si>
+  <si>
+    <t>נאור אקדמי דרופשיפינג</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noamtzur_/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏נועם צור | מאמן פיננסי לזוגות צעירים‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/guylsmedia/</t>
+  </si>
+  <si>
+    <t>נער עסק של סרטונים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/amit_shi_/</t>
+  </si>
+  <si>
+    <t>עמית שמעוני שיווק נער</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tanchum_ran/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏תנחום רן שליחובסקי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/assaf_itzhaki/</t>
+  </si>
+  <si>
+    <t>אסף יצחקי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asafmoryosef/</t>
+  </si>
+  <si>
+    <t>אסף מור יוסף</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/erezbirenboyim/</t>
+  </si>
+  <si>
+    <t>ארז בירנבוים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benbenbaruch/</t>
+  </si>
+  <si>
+    <t>בן בן ברוך</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/daniel.golfur.standup/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דניאל גולפור סטנדאפ  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/henccohen/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חן כהן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/motyaharo/</t>
+  </si>
+  <si>
+    <t>מוטי אהרונוביץ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/matanperetz___/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מתן פרץ‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omerkoly/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏עומר קולי סטנדאפ  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/garinialon/</t>
+  </si>
+  <si>
+    <t>אלון גרעיני</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tal.phone/</t>
+  </si>
+  <si>
+    <t>טל פון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yahavguetta/</t>
+  </si>
+  <si>
+    <t>יהב גואטה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yahavtrosman/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יהב טרוסמן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yam.olisker.yt/</t>
+  </si>
+  <si>
+    <t>ים אוליסקר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/inon_ben_shushan/</t>
+  </si>
+  <si>
+    <t>ינון בן שושן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lina.tech.flat/</t>
+  </si>
+  <si>
+    <t>לינה טק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hardware_x/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎מישל מחשבים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omri.barak/</t>
+  </si>
+  <si>
+    <t>עומרי ברק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idanoren_tech/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏עידן אורן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/phonex.k7/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פון איקס‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/katya_pavlov/</t>
+  </si>
+  <si>
+    <t>קטיה פבלוב בחורה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/netka20/</t>
+  </si>
+  <si>
+    <t>אמה טיפים ועוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_rosenberg/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏בר רוזנברג‏ מעצבת בית </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/veredelkayam/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ורד אלקיים סדר וניקיון‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zeprakti/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏זה פרקטי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/loren.mor/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏לורן מור טיפים ועוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/__morbenaim__/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מור בנעים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/cleanwithtal/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ניקיון | עיצוב הבית | סדר | ארגון‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/karin.handyt/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏קרין קקון - הנדית - יוצרת תוכן - </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/the_home_land/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏שָׁנִיר חן - עיצוב הבית | סדר וארגון </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ohad.the.nomad</t>
+  </si>
+  <si>
+    <t>אוהד הנווד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/uri_liron/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אורי לירון | נווד במשרה מלאה </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/arielron12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אריאל רון‏ מטייל טרמפים ועוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mayalisker/</t>
+  </si>
+  <si>
+    <t>בחורה בעלת סוכנות נסיעות והתמכרות לטיסות‏‎✈️</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/you.like.travel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חובב משאות - אנגלית </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hen.yoseff/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חן יוסף טיולים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/flying.tali/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎טלי כהן טיילנית </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liav.bohbot/</t>
+  </si>
+  <si>
+    <t>‏‎עוזר לכם לטייל🌏 יוצר תוכן בחור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ilay.stoller/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏קומיקאי אילי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nevo.amrani/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> כוכב מצחיק - ילד ישראלי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/donev1_/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎דויד דונב, סרטוני הומור, </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jonathan.keren/</t>
+  </si>
+  <si>
+    <t>יונתן קרן בדרן ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/elai_shamsian23/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏שמסי‏ קומיקאי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/arad_shemi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ארד שמי הומור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dvir33/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎דביר איילת-השחר הומור ועוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shalevbagrish/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎שלו בגריש הומור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asaf.gothelf/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אסף גוטלף בחור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itamarerenberg/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎איתמר ארנברג </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dvir.turjman/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דביר תורג'מן‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yuvaliron/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יובל בדיחות אבא ברחוב </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ben_avraham_10/</t>
+  </si>
+  <si>
+    <t>בן אברן משחקי חברה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/stavasraf91/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎סתיו אסרף הומור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dudi_friedman/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">דודי פרדימן חסיד מעריץ זמרים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakov__azulay/</t>
+  </si>
+  <si>
+    <t>יעקב אזולאי - אורגניסט חרדי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/djamirambl/</t>
+  </si>
+  <si>
+    <t>עמירם בן לולו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meni_hollender/</t>
+  </si>
+  <si>
+    <t>מני הולנדר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asher_grayber/</t>
+  </si>
+  <si>
+    <t>אשר גרייבר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mhasidim/</t>
+  </si>
+  <si>
+    <t>מרדכי חסידים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israelbograd2/</t>
+  </si>
+  <si>
+    <t>ישראל בוגרד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel_cohen_news/</t>
+  </si>
+  <si>
+    <t>ישראל כהן חרדי איש תקשורת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meny_shifman22/</t>
+  </si>
+  <si>
+    <t>מני שיפמן ביתר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/motizalmanov/</t>
+  </si>
+  <si>
+    <t>מוטי זלמנוב כוכב חרדי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yesi.dya/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ידידיה אפשטיין 💥💫חשבון אישי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haravmargalit/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב יהושע מרגלית - העמוד הרשמי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/efiskako/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אפי סקקובסקי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avidror9/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אבי דרור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yochanan_uri/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יוחנן אורי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/aviel_uda/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אביאל עודה דוגמן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avinoam.d/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אבינועם דריקס </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itzik_ohana_/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏איציק אוחנה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ze_lama/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מלך זילבר שלג </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakireisner/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יעקי רייסנר וורט </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shiner_music/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎שיינר מפיק דתי של איתי דוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benytoker2/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏בני טוקר‏ עיתונאי דתי  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shlomigil/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏שלומי גיל‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mendiroth/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מענדל ראטה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asdfg_hjk3179/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הערשי אייזנשטיין‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shmuel.akerman/</t>
+  </si>
+  <si>
+    <t>שמואל אקרמן דתי | שיווק וסרטונים לזמרים | הפקות קאברים | זמר ויוצר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/menachem.toker/</t>
+  </si>
+  <si>
+    <t>מנחם טוקר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dudikepler/</t>
+  </si>
+  <si>
+    <t>דודי קפלר הפרופסור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/david_gurwitz/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎דוד גורביץ דתי אבא </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/david_dbx1/</t>
+  </si>
+  <si>
+    <t>דודו בניאק בחור דתי מבני ברק מעריץ של שרק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shimi_boki/</t>
+  </si>
+  <si>
+    <t>‎שימי בקשפן בחור חסיד‎ (@shimi_boki) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haravigalcohen10/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב יגאל כהן‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haravigalcohen_shiorim/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב יגאל כהן-רשמי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haravfanger/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב יצחק פנגר‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rav_shalom__arush/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב שלום ארוש- גן האמונה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lionelrobine/</t>
+  </si>
+  <si>
+    <t>ליונלרובין יוצר תוכן לזיכוי הרבים</t>
   </si>
 </sst>
 </file>
@@ -971,11 +3791,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314C898-9C37-4B5F-A425-225D45F41FA8}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B495"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="31.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -988,18 +3808,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1012,45 +3832,3864 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-    </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
+      <c r="A9" t="s">
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>112</v>
+      </c>
+      <c r="B63" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>114</v>
+      </c>
+      <c r="B65" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>115</v>
+      </c>
+      <c r="B66" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>116</v>
+      </c>
+      <c r="B67" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>117</v>
+      </c>
+      <c r="B68" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>118</v>
+      </c>
+      <c r="B69" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>120</v>
+      </c>
+      <c r="B72" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>121</v>
+      </c>
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>122</v>
+      </c>
+      <c r="B74" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>123</v>
+      </c>
+      <c r="B75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>124</v>
+      </c>
+      <c r="B76" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>125</v>
+      </c>
+      <c r="B77" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>127</v>
+      </c>
+      <c r="B79" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>128</v>
+      </c>
+      <c r="B80" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>129</v>
+      </c>
+      <c r="B81" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>130</v>
+      </c>
+      <c r="B82" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>131</v>
+      </c>
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>132</v>
+      </c>
+      <c r="B84" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>133</v>
+      </c>
+      <c r="B85" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>134</v>
+      </c>
+      <c r="B86" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>114</v>
+      </c>
+      <c r="B87" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>135</v>
+      </c>
+      <c r="B89" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>137</v>
+      </c>
+      <c r="B92" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>138</v>
+      </c>
+      <c r="B93" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>139</v>
+      </c>
+      <c r="B94" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>177</v>
+      </c>
+      <c r="B98" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>179</v>
+      </c>
+      <c r="B99" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>183</v>
+      </c>
+      <c r="B101" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>185</v>
+      </c>
+      <c r="B102" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>189</v>
+      </c>
+      <c r="B104" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>191</v>
+      </c>
+      <c r="B105" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>193</v>
+      </c>
+      <c r="B106" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>195</v>
+      </c>
+      <c r="B107" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>197</v>
+      </c>
+      <c r="B108" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>199</v>
+      </c>
+      <c r="B109" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>201</v>
+      </c>
+      <c r="B110" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>203</v>
+      </c>
+      <c r="B111" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>205</v>
+      </c>
+      <c r="B112" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>207</v>
+      </c>
+      <c r="B113" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>209</v>
+      </c>
+      <c r="B114" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>211</v>
+      </c>
+      <c r="B115" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>213</v>
+      </c>
+      <c r="B116" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>215</v>
+      </c>
+      <c r="B117" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>217</v>
+      </c>
+      <c r="B118" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>219</v>
+      </c>
+      <c r="B119" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>221</v>
+      </c>
+      <c r="B120" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>223</v>
+      </c>
+      <c r="B121" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>225</v>
+      </c>
+      <c r="B122" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>227</v>
+      </c>
+      <c r="B123" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>229</v>
+      </c>
+      <c r="B124" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>231</v>
+      </c>
+      <c r="B125" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>233</v>
+      </c>
+      <c r="B126" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>235</v>
+      </c>
+      <c r="B127" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>237</v>
+      </c>
+      <c r="B128" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>239</v>
+      </c>
+      <c r="B129" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>241</v>
+      </c>
+      <c r="B130" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>243</v>
+      </c>
+      <c r="B131" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>245</v>
+      </c>
+      <c r="B132" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>247</v>
+      </c>
+      <c r="B133" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>249</v>
+      </c>
+      <c r="B134" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>251</v>
+      </c>
+      <c r="B135" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>253</v>
+      </c>
+      <c r="B136" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>255</v>
+      </c>
+      <c r="B137" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>257</v>
+      </c>
+      <c r="B138" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>259</v>
+      </c>
+      <c r="B139" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>261</v>
+      </c>
+      <c r="B140" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>263</v>
+      </c>
+      <c r="B141" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>265</v>
+      </c>
+      <c r="B142" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>267</v>
+      </c>
+      <c r="B143" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>269</v>
+      </c>
+      <c r="B144" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>271</v>
+      </c>
+      <c r="B145" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>273</v>
+      </c>
+      <c r="B146" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>275</v>
+      </c>
+      <c r="B147" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>277</v>
+      </c>
+      <c r="B148" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>279</v>
+      </c>
+      <c r="B149" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>281</v>
+      </c>
+      <c r="B150" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>283</v>
+      </c>
+      <c r="B151" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>285</v>
+      </c>
+      <c r="B152" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>287</v>
+      </c>
+      <c r="B153" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>289</v>
+      </c>
+      <c r="B154" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>291</v>
+      </c>
+      <c r="B155" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>293</v>
+      </c>
+      <c r="B156" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>295</v>
+      </c>
+      <c r="B157" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>297</v>
+      </c>
+      <c r="B158" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>299</v>
+      </c>
+      <c r="B159" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>301</v>
+      </c>
+      <c r="B160" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>303</v>
+      </c>
+      <c r="B161" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>305</v>
+      </c>
+      <c r="B162" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>307</v>
+      </c>
+      <c r="B163" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>309</v>
+      </c>
+      <c r="B164" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>311</v>
+      </c>
+      <c r="B165" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>305</v>
+      </c>
+      <c r="B166" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>314</v>
+      </c>
+      <c r="B167" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>316</v>
+      </c>
+      <c r="B168" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>318</v>
+      </c>
+      <c r="B169" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>320</v>
+      </c>
+      <c r="B170" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>322</v>
+      </c>
+      <c r="B171" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>324</v>
+      </c>
+      <c r="B172" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>326</v>
+      </c>
+      <c r="B173" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>328</v>
+      </c>
+      <c r="B174" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>330</v>
+      </c>
+      <c r="B175" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>332</v>
+      </c>
+      <c r="B176" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>334</v>
+      </c>
+      <c r="B177" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>336</v>
+      </c>
+      <c r="B178" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>338</v>
+      </c>
+      <c r="B179" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>340</v>
+      </c>
+      <c r="B180" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>342</v>
+      </c>
+      <c r="B181" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>344</v>
+      </c>
+      <c r="B182" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>346</v>
+      </c>
+      <c r="B183" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>348</v>
+      </c>
+      <c r="B184" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>350</v>
+      </c>
+      <c r="B185" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>351</v>
+      </c>
+      <c r="B187" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>353</v>
+      </c>
+      <c r="B188" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>355</v>
+      </c>
+      <c r="B189" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>357</v>
+      </c>
+      <c r="B190" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>359</v>
+      </c>
+      <c r="B191" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>361</v>
+      </c>
+      <c r="B192" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>363</v>
+      </c>
+      <c r="B193" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>365</v>
+      </c>
+      <c r="B194" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>367</v>
+      </c>
+      <c r="B195" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>369</v>
+      </c>
+      <c r="B196" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>371</v>
+      </c>
+      <c r="B197" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>373</v>
+      </c>
+      <c r="B198" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>375</v>
+      </c>
+      <c r="B199" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>377</v>
+      </c>
+      <c r="B200" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>379</v>
+      </c>
+      <c r="B201" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>381</v>
+      </c>
+      <c r="B202" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>383</v>
+      </c>
+      <c r="B203" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>385</v>
+      </c>
+      <c r="B204" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>387</v>
+      </c>
+      <c r="B205" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>389</v>
+      </c>
+      <c r="B206" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>391</v>
+      </c>
+      <c r="B207" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>393</v>
+      </c>
+      <c r="B208" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>395</v>
+      </c>
+      <c r="B209" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>397</v>
+      </c>
+      <c r="B210" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>399</v>
+      </c>
+      <c r="B211" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>401</v>
+      </c>
+      <c r="B212" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>403</v>
+      </c>
+      <c r="B213" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>405</v>
+      </c>
+      <c r="B214" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>407</v>
+      </c>
+      <c r="B215" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>409</v>
+      </c>
+      <c r="B217" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>411</v>
+      </c>
+      <c r="B218" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>413</v>
+      </c>
+      <c r="B219" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>415</v>
+      </c>
+      <c r="B220" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>417</v>
+      </c>
+      <c r="B221" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>419</v>
+      </c>
+      <c r="B222" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>421</v>
+      </c>
+      <c r="B223" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>423</v>
+      </c>
+      <c r="B224" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>425</v>
+      </c>
+      <c r="B225" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>427</v>
+      </c>
+      <c r="B226" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>429</v>
+      </c>
+      <c r="B227" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>431</v>
+      </c>
+      <c r="B228" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>433</v>
+      </c>
+      <c r="B229" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>435</v>
+      </c>
+      <c r="B230" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>437</v>
+      </c>
+      <c r="B231" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>439</v>
+      </c>
+      <c r="B232" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>441</v>
+      </c>
+      <c r="B233" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>443</v>
+      </c>
+      <c r="B234" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>445</v>
+      </c>
+      <c r="B235" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>447</v>
+      </c>
+      <c r="B236" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>449</v>
+      </c>
+      <c r="B237" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>450</v>
+      </c>
+      <c r="B238" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>452</v>
+      </c>
+      <c r="B239" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>454</v>
+      </c>
+      <c r="B240" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>456</v>
+      </c>
+      <c r="B241" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>458</v>
+      </c>
+      <c r="B242" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>460</v>
+      </c>
+      <c r="B243" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>462</v>
+      </c>
+      <c r="B244" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>464</v>
+      </c>
+      <c r="B245" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>466</v>
+      </c>
+      <c r="B246" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>468</v>
+      </c>
+      <c r="B247" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>470</v>
+      </c>
+      <c r="B248" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>472</v>
+      </c>
+      <c r="B249" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>474</v>
+      </c>
+      <c r="B250" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>476</v>
+      </c>
+      <c r="B251" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>478</v>
+      </c>
+      <c r="B252" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>480</v>
+      </c>
+      <c r="B253" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>482</v>
+      </c>
+      <c r="B254" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>484</v>
+      </c>
+      <c r="B255" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>486</v>
+      </c>
+      <c r="B256" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>488</v>
+      </c>
+      <c r="B257" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>490</v>
+      </c>
+      <c r="B258" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>492</v>
+      </c>
+      <c r="B259" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>494</v>
+      </c>
+      <c r="B260" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>496</v>
+      </c>
+      <c r="B261" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>498</v>
+      </c>
+      <c r="B262" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>500</v>
+      </c>
+      <c r="B263" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>502</v>
+      </c>
+      <c r="B264" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>504</v>
+      </c>
+      <c r="B265" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>506</v>
+      </c>
+      <c r="B266" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>508</v>
+      </c>
+      <c r="B267" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>510</v>
+      </c>
+      <c r="B268" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>512</v>
+      </c>
+      <c r="B269" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>514</v>
+      </c>
+      <c r="B270" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>516</v>
+      </c>
+      <c r="B271" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>518</v>
+      </c>
+      <c r="B272" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>520</v>
+      </c>
+      <c r="B273" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>522</v>
+      </c>
+      <c r="B274" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>524</v>
+      </c>
+      <c r="B275" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>526</v>
+      </c>
+      <c r="B276" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>528</v>
+      </c>
+      <c r="B277" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>530</v>
+      </c>
+      <c r="B278" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>532</v>
+      </c>
+      <c r="B279" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>534</v>
+      </c>
+      <c r="B280" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>536</v>
+      </c>
+      <c r="B281" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>538</v>
+      </c>
+      <c r="B282" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>540</v>
+      </c>
+      <c r="B283" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>542</v>
+      </c>
+      <c r="B284" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>544</v>
+      </c>
+      <c r="B285" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>546</v>
+      </c>
+      <c r="B286" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>548</v>
+      </c>
+      <c r="B287" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>550</v>
+      </c>
+      <c r="B288" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>552</v>
+      </c>
+      <c r="B289" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>554</v>
+      </c>
+      <c r="B290" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>556</v>
+      </c>
+      <c r="B291" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>558</v>
+      </c>
+      <c r="B292" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>560</v>
+      </c>
+      <c r="B293" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>562</v>
+      </c>
+      <c r="B294" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>564</v>
+      </c>
+      <c r="B295" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>215</v>
+      </c>
+      <c r="B296" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>567</v>
+      </c>
+      <c r="B297" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>569</v>
+      </c>
+      <c r="B298" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>571</v>
+      </c>
+      <c r="B299" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>573</v>
+      </c>
+      <c r="B300" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>575</v>
+      </c>
+      <c r="B301" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>577</v>
+      </c>
+      <c r="B302" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>579</v>
+      </c>
+      <c r="B303" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>581</v>
+      </c>
+      <c r="B304" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>583</v>
+      </c>
+      <c r="B305" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>585</v>
+      </c>
+      <c r="B306" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>587</v>
+      </c>
+      <c r="B307" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>589</v>
+      </c>
+      <c r="B308" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>591</v>
+      </c>
+      <c r="B309" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>593</v>
+      </c>
+      <c r="B310" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>595</v>
+      </c>
+      <c r="B311" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>597</v>
+      </c>
+      <c r="B312" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" t="s">
+        <v>599</v>
+      </c>
+      <c r="B313" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" t="s">
+        <v>601</v>
+      </c>
+      <c r="B314" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" t="s">
+        <v>603</v>
+      </c>
+      <c r="B315" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" t="s">
+        <v>605</v>
+      </c>
+      <c r="B316" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" t="s">
+        <v>607</v>
+      </c>
+      <c r="B317" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" t="s">
+        <v>609</v>
+      </c>
+      <c r="B318" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" t="s">
+        <v>611</v>
+      </c>
+      <c r="B319" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
+        <v>613</v>
+      </c>
+      <c r="B320" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321" t="s">
+        <v>615</v>
+      </c>
+      <c r="B321" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322" t="s">
+        <v>617</v>
+      </c>
+      <c r="B322" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323" t="s">
+        <v>619</v>
+      </c>
+      <c r="B323" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324" t="s">
+        <v>621</v>
+      </c>
+      <c r="B324" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325" t="s">
+        <v>623</v>
+      </c>
+      <c r="B325" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326" t="s">
+        <v>625</v>
+      </c>
+      <c r="B326" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327" t="s">
+        <v>627</v>
+      </c>
+      <c r="B327" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A328" t="s">
+        <v>629</v>
+      </c>
+      <c r="B328" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A329" t="s">
+        <v>631</v>
+      </c>
+      <c r="B329" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A330" t="s">
+        <v>633</v>
+      </c>
+      <c r="B330" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A331" t="s">
+        <v>635</v>
+      </c>
+      <c r="B331" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>637</v>
+      </c>
+      <c r="B332" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A333" t="s">
+        <v>639</v>
+      </c>
+      <c r="B333" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A334" t="s">
+        <v>641</v>
+      </c>
+      <c r="B334" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A335" t="s">
+        <v>643</v>
+      </c>
+      <c r="B335" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A336" t="s">
+        <v>645</v>
+      </c>
+      <c r="B336" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>647</v>
+      </c>
+      <c r="B337" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>649</v>
+      </c>
+      <c r="B338" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>651</v>
+      </c>
+      <c r="B339" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>653</v>
+      </c>
+      <c r="B340" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>655</v>
+      </c>
+      <c r="B341" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>657</v>
+      </c>
+      <c r="B342" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>659</v>
+      </c>
+      <c r="B343" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>661</v>
+      </c>
+      <c r="B344" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A345" t="s">
+        <v>663</v>
+      </c>
+      <c r="B345" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A346" t="s">
+        <v>665</v>
+      </c>
+      <c r="B346" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A347" t="s">
+        <v>667</v>
+      </c>
+      <c r="B347" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A349" t="s">
+        <v>669</v>
+      </c>
+      <c r="B349" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>671</v>
+      </c>
+      <c r="B350" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>673</v>
+      </c>
+      <c r="B351" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
+        <v>675</v>
+      </c>
+      <c r="B352" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A353" t="s">
+        <v>677</v>
+      </c>
+      <c r="B353" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
+        <v>679</v>
+      </c>
+      <c r="B354" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
+        <v>681</v>
+      </c>
+      <c r="B355" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356" t="s">
+        <v>683</v>
+      </c>
+      <c r="B356" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357" t="s">
+        <v>685</v>
+      </c>
+      <c r="B357" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A358" t="s">
+        <v>687</v>
+      </c>
+      <c r="B358" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359" t="s">
+        <v>689</v>
+      </c>
+      <c r="B359" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A360" t="s">
+        <v>691</v>
+      </c>
+      <c r="B360" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A361" t="s">
+        <v>693</v>
+      </c>
+      <c r="B361" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A362" t="s">
+        <v>695</v>
+      </c>
+      <c r="B362" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A363" t="s">
+        <v>697</v>
+      </c>
+      <c r="B363" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
+        <v>699</v>
+      </c>
+      <c r="B364" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365" t="s">
+        <v>675</v>
+      </c>
+      <c r="B365" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366" t="s">
+        <v>702</v>
+      </c>
+      <c r="B366" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
+        <v>704</v>
+      </c>
+      <c r="B367" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
+        <v>706</v>
+      </c>
+      <c r="B368" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369" t="s">
+        <v>708</v>
+      </c>
+      <c r="B369" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370" t="s">
+        <v>710</v>
+      </c>
+      <c r="B370" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371" t="s">
+        <v>712</v>
+      </c>
+      <c r="B371" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372" t="s">
+        <v>714</v>
+      </c>
+      <c r="B372" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374" t="s">
+        <v>716</v>
+      </c>
+      <c r="B374" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375" t="s">
+        <v>718</v>
+      </c>
+      <c r="B375" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376" t="s">
+        <v>720</v>
+      </c>
+      <c r="B376" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377" t="s">
+        <v>722</v>
+      </c>
+      <c r="B377" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
+        <v>724</v>
+      </c>
+      <c r="B378" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>726</v>
+      </c>
+      <c r="B379" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>728</v>
+      </c>
+      <c r="B380" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>730</v>
+      </c>
+      <c r="B381" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>732</v>
+      </c>
+      <c r="B382" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>734</v>
+      </c>
+      <c r="B383" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>736</v>
+      </c>
+      <c r="B384" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>738</v>
+      </c>
+      <c r="B385" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>740</v>
+      </c>
+      <c r="B386" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>742</v>
+      </c>
+      <c r="B387" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>744</v>
+      </c>
+      <c r="B388" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>746</v>
+      </c>
+      <c r="B389" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>748</v>
+      </c>
+      <c r="B390" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>750</v>
+      </c>
+      <c r="B391" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>752</v>
+      </c>
+      <c r="B392" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>754</v>
+      </c>
+      <c r="B393" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>756</v>
+      </c>
+      <c r="B394" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>758</v>
+      </c>
+      <c r="B395" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>760</v>
+      </c>
+      <c r="B396" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>762</v>
+      </c>
+      <c r="B397" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>764</v>
+      </c>
+      <c r="B398" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>766</v>
+      </c>
+      <c r="B399" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>768</v>
+      </c>
+      <c r="B400" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>770</v>
+      </c>
+      <c r="B401" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>772</v>
+      </c>
+      <c r="B402" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403" t="s">
+        <v>774</v>
+      </c>
+      <c r="B403" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>776</v>
+      </c>
+      <c r="B404" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
+        <v>778</v>
+      </c>
+      <c r="B405" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
+        <v>780</v>
+      </c>
+      <c r="B406" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>782</v>
+      </c>
+      <c r="B407" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>784</v>
+      </c>
+      <c r="B408" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
+        <v>786</v>
+      </c>
+      <c r="B409" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
+        <v>788</v>
+      </c>
+      <c r="B410" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
+        <v>790</v>
+      </c>
+      <c r="B411" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
+        <v>792</v>
+      </c>
+      <c r="B412" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A413" t="s">
+        <v>794</v>
+      </c>
+      <c r="B413" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A414" t="s">
+        <v>796</v>
+      </c>
+      <c r="B414" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A415" t="s">
+        <v>798</v>
+      </c>
+      <c r="B415" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A416" t="s">
+        <v>800</v>
+      </c>
+      <c r="B416" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>802</v>
+      </c>
+      <c r="B417" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A418" t="s">
+        <v>804</v>
+      </c>
+      <c r="B418" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A419" t="s">
+        <v>806</v>
+      </c>
+      <c r="B419" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A420" t="s">
+        <v>808</v>
+      </c>
+      <c r="B420" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A421" t="s">
+        <v>810</v>
+      </c>
+      <c r="B421" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A422" t="s">
+        <v>810</v>
+      </c>
+      <c r="B422" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A423" t="s">
+        <v>812</v>
+      </c>
+      <c r="B423" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
+        <v>814</v>
+      </c>
+      <c r="B424" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
+        <v>816</v>
+      </c>
+      <c r="B425" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
+        <v>818</v>
+      </c>
+      <c r="B426" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
+        <v>820</v>
+      </c>
+      <c r="B427" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
+        <v>822</v>
+      </c>
+      <c r="B428" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A429" t="s">
+        <v>824</v>
+      </c>
+      <c r="B429" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>826</v>
+      </c>
+      <c r="B430" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>828</v>
+      </c>
+      <c r="B431" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
+        <v>830</v>
+      </c>
+      <c r="B432" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>832</v>
+      </c>
+      <c r="B433" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>834</v>
+      </c>
+      <c r="B434" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>836</v>
+      </c>
+      <c r="B435" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>838</v>
+      </c>
+      <c r="B436" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
+        <v>840</v>
+      </c>
+      <c r="B437" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A438" t="s">
+        <v>842</v>
+      </c>
+      <c r="B438" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A439" t="s">
+        <v>844</v>
+      </c>
+      <c r="B439" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>846</v>
+      </c>
+      <c r="B440" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A441" t="s">
+        <v>848</v>
+      </c>
+      <c r="B441" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A442" t="s">
+        <v>850</v>
+      </c>
+      <c r="B442" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A443" t="s">
+        <v>852</v>
+      </c>
+      <c r="B443" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A444" t="s">
+        <v>854</v>
+      </c>
+      <c r="B444" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A445" t="s">
+        <v>856</v>
+      </c>
+      <c r="B445" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A446" t="s">
+        <v>858</v>
+      </c>
+      <c r="B446" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A447" t="s">
+        <v>860</v>
+      </c>
+      <c r="B447" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>862</v>
+      </c>
+      <c r="B448" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>864</v>
+      </c>
+      <c r="B449" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>866</v>
+      </c>
+      <c r="B450" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>868</v>
+      </c>
+      <c r="B451" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>870</v>
+      </c>
+      <c r="B452" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>872</v>
+      </c>
+      <c r="B453" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>874</v>
+      </c>
+      <c r="B454" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>876</v>
+      </c>
+      <c r="B455" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>878</v>
+      </c>
+      <c r="B456" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>880</v>
+      </c>
+      <c r="B457" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>882</v>
+      </c>
+      <c r="B458" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>884</v>
+      </c>
+      <c r="B459" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>261</v>
+      </c>
+      <c r="B460" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>886</v>
+      </c>
+      <c r="B461" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>888</v>
+      </c>
+      <c r="B462" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>890</v>
+      </c>
+      <c r="B463" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>892</v>
+      </c>
+      <c r="B464" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>894</v>
+      </c>
+      <c r="B465" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>896</v>
+      </c>
+      <c r="B466" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>898</v>
+      </c>
+      <c r="B467" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>900</v>
+      </c>
+      <c r="B468" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>902</v>
+      </c>
+      <c r="B469" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>904</v>
+      </c>
+      <c r="B470" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>906</v>
+      </c>
+      <c r="B471" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>908</v>
+      </c>
+      <c r="B472" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>910</v>
+      </c>
+      <c r="B473" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>912</v>
+      </c>
+      <c r="B474" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A475" t="s">
+        <v>914</v>
+      </c>
+      <c r="B475" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A476" t="s">
+        <v>916</v>
+      </c>
+      <c r="B476" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A477" t="s">
+        <v>918</v>
+      </c>
+      <c r="B477" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A478" t="s">
+        <v>920</v>
+      </c>
+      <c r="B478" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A479" t="s">
+        <v>922</v>
+      </c>
+      <c r="B479" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A480" t="s">
+        <v>924</v>
+      </c>
+      <c r="B480" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>926</v>
+      </c>
+      <c r="B481" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>928</v>
+      </c>
+      <c r="B482" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>930</v>
+      </c>
+      <c r="B483" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>932</v>
+      </c>
+      <c r="B484" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>934</v>
+      </c>
+      <c r="B485" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>936</v>
+      </c>
+      <c r="B486" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A487" t="s">
+        <v>938</v>
+      </c>
+      <c r="B487" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A488" t="s">
+        <v>940</v>
+      </c>
+      <c r="B488" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>942</v>
+      </c>
+      <c r="B489" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A490" t="s">
+        <v>944</v>
+      </c>
+      <c r="B490" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A491" t="s">
+        <v>946</v>
+      </c>
+      <c r="B491" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A492" t="s">
+        <v>948</v>
+      </c>
+      <c r="B492" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A493" t="s">
+        <v>950</v>
+      </c>
+      <c r="B493" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A494" t="s">
+        <v>952</v>
+      </c>
+      <c r="B494" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A495" t="s">
+        <v>954</v>
+      </c>
+      <c r="B495" t="s">
+        <v>955</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A9" r:id="rId1" xr:uid="{EE038DAE-04C8-47BE-8F15-E502A8E36DA6}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{B2FECCC5-FAF8-407D-8016-358AD744B92A}"/>
+    <hyperlink ref="A14" r:id="rId2" xr:uid="{A671A1D5-E943-4EA2-9220-0055F332FE00}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/usernames.xlsx
+++ b/usernames.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 אברהם סי\02 לגבות תמיד לענן\תוכנות בשימוש\01 ישן\instagram-stories-to-dropbox\instagram-stories-to-dropbox\instagram-stories-to-dropbox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user-01\Downloads\01 ניתן למחוק\יוזרים אינסטגרם להורדה אוטומטית\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390BA755-763C-41B0-B7FA-1A70CC338A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DF8BFF-6A45-4DC0-846B-AC1CA42DE795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{415E9CA0-5356-4392-A35C-F0C9B70540A1}"/>
   </bookViews>
@@ -33,12 +33,2874 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="956">
   <si>
     <t>username</t>
   </si>
   <si>
     <t>display_name</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/djyochaiedri/</t>
+  </si>
+  <si>
+    <t>יוחאי אדרי די ג'י</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meni_music/</t>
+  </si>
+  <si>
+    <t>מני ראב די ג'יי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avishairosen/</t>
+  </si>
+  <si>
+    <t>אבישי רוזן זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/musicbylufi/</t>
+  </si>
+  <si>
+    <t>לופי זמר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/elnatansh/</t>
+  </si>
+  <si>
+    <t>אלנתן זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yedidyashpizada/</t>
+  </si>
+  <si>
+    <t>ידידיה שפיזדה חבר של נתן מזרחי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lidor___yosef/</t>
+  </si>
+  <si>
+    <t>לידור יוסף זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shilo_elia_/</t>
+  </si>
+  <si>
+    <t>שילה אליה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hen_neeman_grayman/</t>
+  </si>
+  <si>
+    <t>חן גריימן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/akiva.official/</t>
+  </si>
+  <si>
+    <t>עקיבא</t>
+  </si>
+  <si>
+    <t>http://www.instagram.com/shirdavidgadasi/</t>
+  </si>
+  <si>
+    <t>שיר דוד גדסי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idan_wilkis/</t>
+  </si>
+  <si>
+    <t>עידן ווילקיס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_natan_mizrachi_/</t>
+  </si>
+  <si>
+    <t>נתן מזרחי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yossef_picasso/</t>
+  </si>
+  <si>
+    <t>יוסף פיקאסו ראפר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_amitmaimon/</t>
+  </si>
+  <si>
+    <t>עמית מימון חבר של נתן מזרחי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shlomo__abraham/</t>
+  </si>
+  <si>
+    <t>שלמה אברהם זמר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nitay_buskila/</t>
+  </si>
+  <si>
+    <t>‎ניתאי בוסקילה נער זמר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itaydavidofficial/</t>
+  </si>
+  <si>
+    <t>איתי דוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haimisraelofficial/</t>
+  </si>
+  <si>
+    <t>חיים ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chaim_zippel_/</t>
+  </si>
+  <si>
+    <t>חיים ציפל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yair_elitzur_official/</t>
+  </si>
+  <si>
+    <t>יאיר אלייצור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yossefbuskila/</t>
+  </si>
+  <si>
+    <t>יוסף חיים בוסקילה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yosefhaimzohar/</t>
+  </si>
+  <si>
+    <t>יוסף חיים זוהר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nussiliberman/</t>
+  </si>
+  <si>
+    <t>נותי ליברמן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/netanelisrael_official/</t>
+  </si>
+  <si>
+    <t>נתנאל ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/srulibroncher/</t>
+  </si>
+  <si>
+    <t>שרולי ברונכר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/qmitsharabi/</t>
+  </si>
+  <si>
+    <t>עמית שרעבי - זמר ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hen_biton44/</t>
+  </si>
+  <si>
+    <t>חן ביטון - ילד זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shay_ben_aroya/</t>
+  </si>
+  <si>
+    <t>שי בן ארויה - זמר ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hananbenariofficial/</t>
+  </si>
+  <si>
+    <t>חנן בן ארי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/inon_eliya/</t>
+  </si>
+  <si>
+    <t>ינון אליה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ilay_avidani/</t>
+  </si>
+  <si>
+    <t>עילי אבידני</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ballagan_sessions/</t>
+  </si>
+  <si>
+    <t>בלגן סשן ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rizika_rap/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏רז נוחיאן‏ ראפר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lee_ovadia/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏לי עובדיה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gilosssssss/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎גיל בנדרלי ראפר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yossef_blueman/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יוסף בלומן זמר דתלש </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eyal_levi_official/</t>
+  </si>
+  <si>
+    <t>אייל לוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liam__golan/</t>
+  </si>
+  <si>
+    <t>ליאם גולן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benaia_barabi/</t>
+  </si>
+  <si>
+    <t>בניה ברבי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/boi_vibe_ish_/</t>
+  </si>
+  <si>
+    <t>וייב איש</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maorelu/</t>
+  </si>
+  <si>
+    <t>מאור ארגוב ראפר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maorashkenazi_/</t>
+  </si>
+  <si>
+    <t>מאור אשכנזי ראפר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dan_avivi_music/</t>
+  </si>
+  <si>
+    <t>דן חביבי חבר של נתן מזרחי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moshe._ohayon/</t>
+  </si>
+  <si>
+    <t>משה אוחיון בחור ראפר דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/chen_porati/</t>
+  </si>
+  <si>
+    <t>חן פורתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ariel._.azulay1/</t>
+  </si>
+  <si>
+    <t>אריאל אזולאי נער זמר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/adir__yakov/</t>
+  </si>
+  <si>
+    <t>אדיר יעקב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/balishag__/</t>
+  </si>
+  <si>
+    <t>באלישג - ראפר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tzukush/</t>
+  </si>
+  <si>
+    <t>צוקוש</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omeradam/</t>
+  </si>
+  <si>
+    <t>עומר אדם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/duda_gang_official/</t>
+  </si>
+  <si>
+    <t>דודא גאנג</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yageloshri1/</t>
+  </si>
+  <si>
+    <t>יגל אושרי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itaylevi7/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yamrefaeli/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/oshercohen/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ilay_elmakys/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal__adam/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yonathan_hertz/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yuval_duda/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/odeyaazoulay/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/boi_vibe_ish_/?hl=en</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_orisaban/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ronhayunofficial/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ravid_plotnik/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liornarkis/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/officialeliad/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yonatankalimi/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maoredriofficial/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nathangoshen/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/static/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/stephane.le.gar/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/edennhason/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idob.official/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shahartavoch/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shreki/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shaharsaul/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sasson_ifram_shaulov/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eyalgolan1/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kfirtsafrir/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nadav_hanzis/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/peled__/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idomalka29/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bartzabary/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ben.zur/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎איתי לוי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ים רפאלי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אושר כהן‏ </t>
+  </si>
+  <si>
+    <t>עילאי אלמקייס</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎גל אדם </t>
+  </si>
+  <si>
+    <t>יונתן הרץ זמר</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דודא‏ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אודיה אזולאי </t>
+  </si>
+  <si>
+    <t xml:space="preserve">וייב איש זמר </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏️אורי סבאן‏ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏רון חיון‏ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">רביד פלוטניק‏ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">בניה ברבי‏ </t>
+  </si>
+  <si>
+    <t>ליאור נרקיס</t>
+  </si>
+  <si>
+    <t>אליעד</t>
+  </si>
+  <si>
+    <t>יונתן קלימי</t>
+  </si>
+  <si>
+    <t>מאור אדרי</t>
+  </si>
+  <si>
+    <t>נתן גושן</t>
+  </si>
+  <si>
+    <t>סטטיק</t>
+  </si>
+  <si>
+    <t>סטפן לגר</t>
+  </si>
+  <si>
+    <t>עדן חסון</t>
+  </si>
+  <si>
+    <t>עידו בי</t>
+  </si>
+  <si>
+    <t>שחר טבוך</t>
+  </si>
+  <si>
+    <t>שרק ראפר</t>
+  </si>
+  <si>
+    <t>שחר סאול</t>
+  </si>
+  <si>
+    <t>ששון שאולוב</t>
+  </si>
+  <si>
+    <t>אייל גולן</t>
+  </si>
+  <si>
+    <t>כפיר צפריר</t>
+  </si>
+  <si>
+    <t>יובל דודה</t>
+  </si>
+  <si>
+    <t>נדב חנציס</t>
+  </si>
+  <si>
+    <t>פלד ראפר</t>
+  </si>
+  <si>
+    <t>עידו מלכה</t>
+  </si>
+  <si>
+    <t>בר צברי</t>
+  </si>
+  <si>
+    <t>בן צור</t>
+  </si>
+  <si>
+    <t>אהבת השם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/or_korem/</t>
+  </si>
+  <si>
+    <t>אור קורם חבר של דילן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idantelem_/</t>
+  </si>
+  <si>
+    <t>אינדה גיים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benkeysar/</t>
+  </si>
+  <si>
+    <t>בן קיסר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rontroyan/</t>
+  </si>
+  <si>
+    <t>רון טרויאן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shaiyomtov/</t>
+  </si>
+  <si>
+    <t>שי יום טוב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/erez_kalderon/</t>
+  </si>
+  <si>
+    <t>ארז קלדרון חטוף</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/grincess_lera/</t>
+  </si>
+  <si>
+    <t>לרה גרינסס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/guy_eitan/</t>
+  </si>
+  <si>
+    <t>גיא איתן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zehavioz/</t>
+  </si>
+  <si>
+    <t>עוז זהבי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benyaminburyevmusic/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">בנימין בורייב מחקה את עדן בן זקן  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yagil_yaakov/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יגיל יעקב חטוף </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/or_yaakov18/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אור יעקו‏ב חטוף  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hapshutaofficial/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הפשוטע‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yotzim/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יותם זמרי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bariysirtonim/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הסרטונים של ברי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/malahi1217/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎מלאכי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal_bargig/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">גל בַרגִיג מעריצה של עדן חסון‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liron_ofir/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎לירון אופיר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jonathan_grosman1/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יהונתן גרוסמן‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itzikreuven10/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎איציק ראובן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omri_hayoon/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏עומרי חיון‏ רכילות </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maxbhman/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מקס בחמן גומי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eladrabi12/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ספר בטיקטוק </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yotam_gavriel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יותם גבריאל חבר של עדן חסון </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yali__moscovith/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">צייר יהלי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eranswis/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ערן סוויסה רכילות  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rahums/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎רחום יוטיובר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nicole_edlind/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ניקול אדלינד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/agamnava1234/?g=5</t>
+  </si>
+  <si>
+    <t>‏גברת שווארמה🐄</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/michael_yosefyan/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מיכאל יוספיאן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/matan_skaytel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מתן סקייטל יוצר דיגיטלי תימני עממי| </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dylendror/</t>
+  </si>
+  <si>
+    <t>דילן דרור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/alex_shults/</t>
+  </si>
+  <si>
+    <t>אלכס שולץ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yonaeshet/</t>
+  </si>
+  <si>
+    <t>יונה אשד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idanshalva/</t>
+  </si>
+  <si>
+    <t>עידן שלוה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yhonatan.shtivi/</t>
+  </si>
+  <si>
+    <t>יונתן שתיוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moshe_korsia/</t>
+  </si>
+  <si>
+    <t>משה כורסיה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nessi_tikshoret_tveria/</t>
+  </si>
+  <si>
+    <t>נסי תקשורת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/galgul_halaly/</t>
+  </si>
+  <si>
+    <t>גלגול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shuki_salomon/</t>
+  </si>
+  <si>
+    <t>שוקי סלומון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/orlasryofficial/</t>
+  </si>
+  <si>
+    <t>אור לסרי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mreviatar/</t>
+  </si>
+  <si>
+    <t>אביתר עוזרי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/alfiguri/</t>
+  </si>
+  <si>
+    <t>גורי אלפי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yankigoldhaber/</t>
+  </si>
+  <si>
+    <t>יענקי גולדהבר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yahli_watson/</t>
+  </si>
+  <si>
+    <t>יהלי ווטסון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yali__gabay</t>
+  </si>
+  <si>
+    <t>יהלי גבאי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liorsuchard/</t>
+  </si>
+  <si>
+    <t>ליאור סושרד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/assiazar/</t>
+  </si>
+  <si>
+    <t>אסי עזר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kobi_drive/</t>
+  </si>
+  <si>
+    <t>קובי כהן מורה נהיגה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/oranatedgi/</t>
+  </si>
+  <si>
+    <t>אורן אטדגי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jonny_hishgozim/</t>
+  </si>
+  <si>
+    <t>ג'וני חישגוזים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/d.pro__/</t>
+  </si>
+  <si>
+    <t>די פרו בונה משאית</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/elad__turgeman/</t>
+  </si>
+  <si>
+    <t>אליעד תורגמן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noya_ashash1/</t>
+  </si>
+  <si>
+    <t>נויה אשש חברה של אייל לוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nadir_eliyahou/</t>
+  </si>
+  <si>
+    <t>נדיר אליהו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/barjeell/?e=884a101e-9b8f-4240-afd7-17196003558e&amp;g=5</t>
+  </si>
+  <si>
+    <t>ברגיל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idan.keret/reels/</t>
+  </si>
+  <si>
+    <t>עידן קרט</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/donev1_/reels/</t>
+  </si>
+  <si>
+    <t>דונב בחור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/edrikobi/?e=a288bb65-06fc-4b56-a7e1-4e3b07fd1753&amp;g=5</t>
+  </si>
+  <si>
+    <t>קובי אדרי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal_zinger/</t>
+  </si>
+  <si>
+    <t>גל זינגר גלשן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yosef.haim10/</t>
+  </si>
+  <si>
+    <t>יוסף חיים סבג בלוגר ננח</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omerkoly/?e=b785a882-b2c7-4ade-ac28-fcfc57ede7e2&amp;g=5</t>
+  </si>
+  <si>
+    <t>עומר קולי מגיב על סרטונים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noam.takla7/</t>
+  </si>
+  <si>
+    <t>נועם טקלה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yali_tattoo/</t>
+  </si>
+  <si>
+    <t>יהלי צייר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tal_shenhav/</t>
+  </si>
+  <si>
+    <t>טל שנהב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omer.yaron/</t>
+  </si>
+  <si>
+    <t>עומר ירון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noamhimself/</t>
+  </si>
+  <si>
+    <t>נועם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/amitsegalnews/</t>
+  </si>
+  <si>
+    <t>עמית סגל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ron.kav/</t>
+  </si>
+  <si>
+    <t>רון קבונסקי</t>
+  </si>
+  <si>
+    <t>עומר הוריון עמוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakirbarzohar/</t>
+  </si>
+  <si>
+    <t>‎יקיר בר זוהר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/giladby__/</t>
+  </si>
+  <si>
+    <t>גיל נער חמוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shonmizrachi/</t>
+  </si>
+  <si>
+    <t>שון מזרחי‎ סטנדאפיסט</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sabantwins_/</t>
+  </si>
+  <si>
+    <t>תאומים מפורסמים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omri.malinsky02/</t>
+  </si>
+  <si>
+    <t>עומרי מלינסקי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omrilevi9/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עומרי לוי‎ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gilelimelech/</t>
+  </si>
+  <si>
+    <t>גיל אלימלך</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rotem_asherov/</t>
+  </si>
+  <si>
+    <t>רותם אשרוב יוטיובר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/isaac.lasry/</t>
+  </si>
+  <si>
+    <t>יצחק לסרי דתי יוטיובר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yonitovim/</t>
+  </si>
+  <si>
+    <t>יוני טובים הומו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yarin_hamevin/</t>
+  </si>
+  <si>
+    <t>ירין מבין</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ohad.avitbul/</t>
+  </si>
+  <si>
+    <t>אוהד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liat_berkovich_kraviz/</t>
+  </si>
+  <si>
+    <t>‎ליאת ברקוביץ קרביץ על שם יקיר בר זוהר סבי ומורי‎ (@liat_berkovich_kraviz) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nirbenilush10/</t>
+  </si>
+  <si>
+    <t>‎ניר בנילוש‎ (@nirbenilush10) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nitay_yona_news/</t>
+  </si>
+  <si>
+    <t>‎הכתב הצעיר - נתאי יונה 📢‎ (@nitay_yona_news) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mrshibolet/</t>
+  </si>
+  <si>
+    <t>מר שיבולת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sniravitan23/</t>
+  </si>
+  <si>
+    <t>‎שניר אביטן‎ (@sniravitan23) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/i_am_the_shadow/</t>
+  </si>
+  <si>
+    <t>הצל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ahavat_goldenboy/?e=1f142175-db05-406d-a147-cbb2e277a09d&amp;g=5</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avia_productions/</t>
+  </si>
+  <si>
+    <t>אביה הפקות מנהל של אלייצור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/or_cohen_keyboard/</t>
+  </si>
+  <si>
+    <t>אור כהן חבר של עדן חסון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avihay.idan/</t>
+  </si>
+  <si>
+    <t>אניווי עידן מנגן על קנון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/assafcohen15/</t>
+  </si>
+  <si>
+    <t>אסף כהן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_kubani/</t>
+  </si>
+  <si>
+    <t>בר הפקות מוזיקאי חבר של יוסף בוסקילה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/guykumusic/</t>
+  </si>
+  <si>
+    <t>גיקו מיוזיק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/david_avraham_carmi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דוד כרמי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/davids__band/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דוד שם טוב‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zeev6356326/</t>
+  </si>
+  <si>
+    <t>זאבי רבינוביץ חבר של שרולי ברונכר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zivnoyman/?e=c8308a4b-88e0-4732-8282-94fcb1eae831&amp;g=5</t>
+  </si>
+  <si>
+    <t>‎זיו נוימן‎ מנגן על קנון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haimshaked_productions/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חיים שקד מפיק של איתי דוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/talforer/</t>
+  </si>
+  <si>
+    <t>טל פורר מפיק אלייצור ועוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakovzeyakov/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יעקב אסרף גיטריסט של ריבו ועוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakir_hiyaev_music/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">יקיר חייאב </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yarin_yacobi/</t>
+  </si>
+  <si>
+    <t>ירין יעקובי מנהל אולפן של שרק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel_elgrabli/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ישראל אלגרבלי | כותב שירים✏️‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mccohen/</t>
+  </si>
+  <si>
+    <t>כהן מפיק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/leibalelipsker/</t>
+  </si>
+  <si>
+    <t>לייבלה ליפסקר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/doronsery/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎מפיק לזמרים דורון סרי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israelr2/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מפיק של זמרים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/moshe.dotan/</t>
+  </si>
+  <si>
+    <t>משה דותן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nuta.levin/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">נוטע לוין מפיק חסידי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noam_akrabi/</t>
+  </si>
+  <si>
+    <t>נועם עקרבי מוזיקאי טכני</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yarinalushstudio/</t>
+  </si>
+  <si>
+    <t>סטודיו ירין אלוש עטיפות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/adiel__cohen/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎עדיאל כהן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/oz_altman/?e=72f92188-1183-4693-8895-1e00e8224989&amp;g=5</t>
+  </si>
+  <si>
+    <t>עוז אלטמן דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/offernissimofficial/?e=cc37f1b4-dc98-4514-86a2-20b783b96383&amp;g=5</t>
+  </si>
+  <si>
+    <t>עופר ניסים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/amit.bracha/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎עמית ברכה זמר ומוזיקאי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_ranicohen/</t>
+  </si>
+  <si>
+    <t>רוני כהן להקת ניגון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sikurim_israel/</t>
+  </si>
+  <si>
+    <t>חדש בעגלה - מוצרים חדשים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mobile1_music/</t>
+  </si>
+  <si>
+    <t>מובייל מיוזיק - חברת מוזיקה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kaspit_art/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כספית ייצוג אמנים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yomi_news/</t>
+  </si>
+  <si>
+    <t>יומי ניוז</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/theking.dylen16/</t>
+  </si>
+  <si>
+    <t>עמוד הערכה לדילן המושלם❤️❤️</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kolbarama/</t>
+  </si>
+  <si>
+    <t>קול ברמה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shticktokofficial/</t>
+  </si>
+  <si>
+    <t>שטיקטוק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nihnaslketzev/?e=7c54d91e-c509-450d-b7dc-e3f41743ee1c&amp;g=5</t>
+  </si>
+  <si>
+    <t>נכנס לקצב - מסיבות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kan_israel/</t>
+  </si>
+  <si>
+    <t>כאן ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hidabroottv/?e=c04f86d4-a924-4df5-8ba1-242c88495591&amp;g=5</t>
+  </si>
+  <si>
+    <t>הידברות טיוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hizukim24/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏חיזוקים_24_‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kuparashit1/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏קופה ראשית‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noshmim.mizrahit/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏נושמים מזרחית‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/flash_news_il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏חדשות פלאש </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hacelebs_shel_hachibur/</t>
+  </si>
+  <si>
+    <t>הסלבס של הציבור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israelissm/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ישראליזם‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/farmax_amisraelhi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎עם ישראל חי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idfonline/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏צהל - צבא ההגנה לישראל‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dos_celebs_/</t>
+  </si>
+  <si>
+    <t>‏דוס סלבס העמוד הרשמי❗</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dos_celebs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דוסלבס סטטוס‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dos_celebs_status/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israeli_songs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏שירים ישראלים העמוד הרשמי🇮🇱‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dati_bidur/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דתי בידור 🌟העמוד הרשמי🌟‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mizrahitpage/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מזרחית באינסטגרם‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/24tv/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ערוץ 24‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/i24news_he/</t>
+  </si>
+  <si>
+    <t>24 ניוז</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lsrael.music/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ישראל מיוזיק‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/big.tora.il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏בּוֹרֵא עוֹלָם תּוֹדָה </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hotbiduronline/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הוט בידור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itmodels/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎סוכנות דוגמנות </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/humor_asor.il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הומור אסור ישראל </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yomsheniofficial/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יום שני </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/justmusic.college/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מכללת ג׳אסט מיוזיק‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel.business/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ישראל ביזנס‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/newsaskan/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏חדשות עסקן‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ronybidortiktok/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏רוני בידור טיקטוק‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tzama_music/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏צמאה | לחיות את הניגון🎶‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rj_veronika7/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אמנות נייר חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/messudarot/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מסודרות | אריזה ופריקה במעבר דירה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ahuz.ehad/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אחוז אחד‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hapitgam/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הפתגם היומי🤍‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/todaxco/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏תודה חולצות </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/apargod_chadashot/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏חדשות הפרגוד‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/apr_god/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הפרגוד‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/olam_il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מסביב לעולם 🌍 יהונתן ואריאל‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/funny.is.healthy/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מצחיק זה בריא🤣‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_electro_beats/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אלקטרו ביטס </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yam_ahzakot/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ים אחזקות | ניהול מבנים | אחזקה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/link__il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏לינק ישראל‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/radiokolyezreel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏רדיו קול יזרעאל | ניו מדיה באקדמיה </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hakufsah/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הקופסה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kirkushim.tb/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏קירקושים אמנות על קירות‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gadgetlandil/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">עולם של גאדג׳טים✨‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/microsoft_rnd_israel/</t>
+  </si>
+  <si>
+    <t>מיקרוסופט ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/today_and_before/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">היום ולפני📆‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/insane_kosherkravi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אינסיין כושר קרבי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pumpi_il/</t>
+  </si>
+  <si>
+    <t>פאמפי‏ פאמפי הדלקן שחוסך ליטרים של זמן וכסף</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/signon_corp/</t>
+  </si>
+  <si>
+    <t>סגנון עמוד ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nishmat_kol_hai_djs/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏נשמת קול חי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/johny.turbo/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כל מה שקשור לעולם המוטורי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/995fm/</t>
+  </si>
+  <si>
+    <t>🔥רדיו 99.5 חם-אש🔥</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/standupfactory/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏סטנדאפ פקטורי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/fixfixfixfix/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חברת בגדים מיניונים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/barangay__/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ברנז׳ה‏ חרדי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hizukim_yomii/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">חיזוקים לזיכוי הרבים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kanmoreshet/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏כאן מורשת‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/joymobile.co.il/</t>
+  </si>
+  <si>
+    <t>חנות טלפונים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eranchen_photographer/</t>
+  </si>
+  <si>
+    <t>ארן חן | צלמים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/abamevich/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אבא מביך‏ </t>
+  </si>
+  <si>
+    <t>http://instagram.com/scopt/</t>
+  </si>
+  <si>
+    <t>חדשות סקופט</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/harabanit/</t>
+  </si>
+  <si>
+    <t>הרבנית</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shmua_bidur/</t>
+  </si>
+  <si>
+    <t>שמועה בידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/datiim_bareshet/</t>
+  </si>
+  <si>
+    <t>דתיים ברשת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/frogifrogi/</t>
+  </si>
+  <si>
+    <t>פרוגי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel_bidur/</t>
+  </si>
+  <si>
+    <t>ישראל בידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/erevtov/</t>
+  </si>
+  <si>
+    <t>ערב טוב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/wallanews/</t>
+  </si>
+  <si>
+    <t>וואלה ניוז</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/wallacelebs/</t>
+  </si>
+  <si>
+    <t>וואלה סלבס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/m_laradar/</t>
+  </si>
+  <si>
+    <t>מתחת לרדאר</t>
+  </si>
+  <si>
+    <t>עומרי חיון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/wallaentertainment/</t>
+  </si>
+  <si>
+    <t>וואלה תרבות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/news.bidur</t>
+  </si>
+  <si>
+    <t>חדשות הבידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hambamedia/</t>
+  </si>
+  <si>
+    <t>חם במדיה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/makocelebs/</t>
+  </si>
+  <si>
+    <t>מאקו סלבס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kan_gimel/</t>
+  </si>
+  <si>
+    <t>כאן גימל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kan_reshetb/</t>
+  </si>
+  <si>
+    <t>כאן רשת ב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kikarhashabat/</t>
+  </si>
+  <si>
+    <t>כיכר השבת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/live_bidur/</t>
+  </si>
+  <si>
+    <t>לייב בידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/artcoeur_israel/</t>
+  </si>
+  <si>
+    <t>ארטקור הפקות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lionmotivationil/</t>
+  </si>
+  <si>
+    <t>משפטים מועדון האריות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/storyill/</t>
+  </si>
+  <si>
+    <t>סטוריל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bardak613/</t>
+  </si>
+  <si>
+    <t>ברדק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shticktokofficial1/</t>
+  </si>
+  <si>
+    <t>שטיקטוק גיבוי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/glglz/</t>
+  </si>
+  <si>
+    <t>גלגלצ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yomtov_tonight/</t>
+  </si>
+  <si>
+    <t>יומטוב טו נייט</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/radar_il/</t>
+  </si>
+  <si>
+    <t>ראדר אי אל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/cattleya_eyewear/</t>
+  </si>
+  <si>
+    <t>קאטלייה טרנדים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/celebs.notifications/</t>
+  </si>
+  <si>
+    <t>עדכוני סלבס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/push.il/</t>
+  </si>
+  <si>
+    <t>פוש חדשות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/pnaiplus/</t>
+  </si>
+  <si>
+    <t>פנאי פלוס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/musiclitonfire_1/</t>
+  </si>
+  <si>
+    <t>סרטוני מוזיקה דתיים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/icon_israel_/</t>
+  </si>
+  <si>
+    <t>אייקון ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/besties.israel/</t>
+  </si>
+  <si>
+    <t>בסטיז בידור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bafront.pr</t>
+  </si>
+  <si>
+    <t>בפרונט דתי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yagil.yaakov.fans/</t>
+  </si>
+  <si>
+    <t>עמוד ליגיל יעקב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel_bidur_gaming/</t>
+  </si>
+  <si>
+    <t>ישראל בידור גיימינג</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israella.music/</t>
+  </si>
+  <si>
+    <t>ישראלה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/booqueen.il/</t>
+  </si>
+  <si>
+    <t>בוקיואין מנהלי הפקות</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/newsfash/</t>
+  </si>
+  <si>
+    <t>חדשות האופנה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/_u.smile_/</t>
+  </si>
+  <si>
+    <t>חיל חיוך</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hazinor/</t>
+  </si>
+  <si>
+    <t>הצינור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tiktokshow_il/</t>
+  </si>
+  <si>
+    <t>טיקטוק שואו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maarivonline/</t>
+  </si>
+  <si>
+    <t>מעריב אונליין</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/keshet12/</t>
+  </si>
+  <si>
+    <t>קשת 12</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ildailymotivation/</t>
+  </si>
+  <si>
+    <t>מוטיבציה יומיומית</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/the_next_step_il/</t>
+  </si>
+  <si>
+    <t>הצעד הבא מוטיבציה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omer_adam_my_life_/</t>
+  </si>
+  <si>
+    <t>עומר אדם מיי לייף עמוד לעומר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sta2sim_metzaitzim</t>
+  </si>
+  <si>
+    <t>סטטוסים מצייצים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/arutz.sheva/reels/</t>
+  </si>
+  <si>
+    <t>ערוץ שבע</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/funny.li.1/reels/</t>
+  </si>
+  <si>
+    <t>לצחוק זה בריא</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hiphopisrael/</t>
+  </si>
+  <si>
+    <t>היפהופ ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/amit.hashai/</t>
+  </si>
+  <si>
+    <t>בחשאי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/audioter_il/</t>
+  </si>
+  <si>
+    <t>אודיותר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/newsil.ontime/</t>
+  </si>
+  <si>
+    <t>חדשות בזמן אמת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/news.0nline/</t>
+  </si>
+  <si>
+    <t>ניוז אונליין</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/halal.il/</t>
+  </si>
+  <si>
+    <t>מסע בחלל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hustle_hub.il/</t>
+  </si>
+  <si>
+    <t>עמוד שמראיין עשירים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lsrael_office/</t>
+  </si>
+  <si>
+    <t>ישראל בידור אופיס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jewish_battle/</t>
+  </si>
+  <si>
+    <t>בטל ראפ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hadmor.il/</t>
+  </si>
+  <si>
+    <t>‎האדמור‎ (@hadmor.il) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rehovtoomtoom/</t>
+  </si>
+  <si>
+    <t>רחוב טומטום</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dorian_parkour/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ספורטאי חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/marssiek/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎צלם חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/marssiek/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎צלם הולנדי חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/thekiryalife/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎קיריה קולסניקוב עושה מתיחות ברחוב חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ai.boysphotograph/</t>
+  </si>
+  <si>
+    <t>‏‎עמוד תמונות גלריית בנים בינה מלאכותית   חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/realadamrose/</t>
+  </si>
+  <si>
+    <t>כוכב בידור חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/troyesivan/</t>
+  </si>
+  <si>
+    <t>טרוי סיוון זמר יהודי אוסטרלי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/learnwithvalerio/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎מדע וטכנולוגיה חול   </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zachchoi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎טבח חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sergio_outdoors/</t>
+  </si>
+  <si>
+    <t>‏‎פטנטים  חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idealizandocoisas/</t>
+  </si>
+  <si>
+    <t>‏‎‏‎תיקונים ופטנטים חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/quick_fix_life_4727/</t>
+  </si>
+  <si>
+    <t>‏‎תיקונים ופטנטים  חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/daniellabelle1/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎סרטונים מגניבים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/loopedlaces/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">קשירת שרוכים חול </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/laivy.miller/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎זמרים יהודים אמריקאים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/abdul_sistem/</t>
+  </si>
+  <si>
+    <t>‏‎טריקים מחשבים  חול</t>
+  </si>
+  <si>
+    <t>עושה קפיצות ועוד חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/parkour_athlete_/</t>
+  </si>
+  <si>
+    <t>חול פרקור ספורטאי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/axelydaniel/</t>
+  </si>
+  <si>
+    <t>אלכס ודניאל זוג חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yuki_nara77/</t>
+  </si>
+  <si>
+    <t>בנות הלבשה תחתונה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/brave.gals/reels/</t>
+  </si>
+  <si>
+    <t>יוצרת תוכן חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gabrielsilva1k/reels/</t>
+  </si>
+  <si>
+    <t>גבריאל סילבה קומיקאי ויוצר  תוכן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tatebutts/?e=fe7174fa-c38e-407e-8ebb-cfc510f91c35&amp;g=5</t>
+  </si>
+  <si>
+    <t>זמר ילד חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/konraddamer/</t>
+  </si>
+  <si>
+    <t>נער חול</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/or_efraim/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אור אפרים שיווק </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ariel.kigel.social.media/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אריאל קיגל </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/virtualmedia.il/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">וירטואל מדיה שיווק </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idoshafirr/</t>
+  </si>
+  <si>
+    <t>עידו שפיר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ofek_hilali/</t>
+  </si>
+  <si>
+    <t>אופק הללי עורך וידאו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/illy_alfia/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אִילִּי אלפיה צלם וולוגר‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/eli_sadeh_videoagapher/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אלי שדה צילום וידאו‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yehonatan5/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎גוני צלם ועורך וידאו </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal_isaev/#</t>
+  </si>
+  <si>
+    <t>גל איסייב</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gal_isaev2/#</t>
+  </si>
+  <si>
+    <t>גל איסייב עמוד שני</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/davidgold.video/</t>
+  </si>
+  <si>
+    <t>דוד גולדשטיין צלם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/___yakirphoto1___/</t>
+  </si>
+  <si>
+    <t>יקיר דהאן צלם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/isaac_kelman_/</t>
+  </si>
+  <si>
+    <t>ישראל קלמן צלם חבר של שרולי ברונכר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/maor_kesem_livshiz/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מאור קסם ליבשיץ | גרפיקאי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meni_3030/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מנחם שאער | צלם סטילס </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/matanmalahovski/</t>
+  </si>
+  <si>
+    <t>מתן מליכובסקי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noamtryber/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏נועם טרייבר </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nirahiel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ניר אחיאל | מעצב גרפי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/the_giant01/</t>
+  </si>
+  <si>
+    <t>נתי תורגמן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/phoenixmedia.official/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פניקס מדיה מפורסמים‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shimi__photos/</t>
+  </si>
+  <si>
+    <t>שימי פוטוס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shneor_shif/</t>
+  </si>
+  <si>
+    <t>שניאור שיף</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/aviya.rosenheim/</t>
+  </si>
+  <si>
+    <t>אבייה רוזנהיים סאס</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/alon_gefen/</t>
+  </si>
+  <si>
+    <t>אלון גפן אוטומציה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/daniel.moldawsky/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎דניאל מולידבסקי דרופשיפינג </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/kristalmediia/</t>
+  </si>
+  <si>
+    <t>דניאל קריסטל נער יזם</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/talecomlaunch/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎טל רוטר איקומרס </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/naorhacmon/</t>
+  </si>
+  <si>
+    <t>נאור אקדמי דרופשיפינג</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noamtzur_/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏נועם צור | מאמן פיננסי לזוגות צעירים‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/guylsmedia/</t>
+  </si>
+  <si>
+    <t>נער עסק של סרטונים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/amit_shi_/</t>
+  </si>
+  <si>
+    <t>עמית שמעוני שיווק נער</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tanchum_ran/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏תנחום רן שליחובסקי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/assaf_itzhaki/</t>
+  </si>
+  <si>
+    <t>אסף יצחקי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asafmoryosef/</t>
+  </si>
+  <si>
+    <t>אסף מור יוסף</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/erezbirenboyim/</t>
+  </si>
+  <si>
+    <t>ארז בירנבוים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benbenbaruch/</t>
+  </si>
+  <si>
+    <t>בן בן ברוך</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/daniel.golfur.standup/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דניאל גולפור סטנדאפ  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/henccohen/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חן כהן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/motyaharo/</t>
+  </si>
+  <si>
+    <t>מוטי אהרונוביץ</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/matanperetz___/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מתן פרץ‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omerkoly/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏עומר קולי סטנדאפ  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/garinialon/</t>
+  </si>
+  <si>
+    <t>אלון גרעיני</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/tal.phone/</t>
+  </si>
+  <si>
+    <t>טל פון</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yahavguetta/</t>
+  </si>
+  <si>
+    <t>יהב גואטה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yahavtrosman/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יהב טרוסמן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yam.olisker.yt/</t>
+  </si>
+  <si>
+    <t>ים אוליסקר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/inon_ben_shushan/</t>
+  </si>
+  <si>
+    <t>ינון בן שושן</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lina.tech.flat/</t>
+  </si>
+  <si>
+    <t>לינה טק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hardware_x/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎מישל מחשבים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/omri.barak/</t>
+  </si>
+  <si>
+    <t>עומרי ברק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/idanoren_tech/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏עידן אורן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/phonex.k7/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">פון איקס‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/katya_pavlov/</t>
+  </si>
+  <si>
+    <t>קטיה פבלוב בחורה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/netka20/</t>
+  </si>
+  <si>
+    <t>אמה טיפים ועוד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bar_rosenberg/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏בר רוזנברג‏ מעצבת בית </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/veredelkayam/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ורד אלקיים סדר וניקיון‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/zeprakti/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏זה פרקטי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/loren.mor/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏לורן מור טיפים ועוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/__morbenaim__/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מור בנעים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/cleanwithtal/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ניקיון | עיצוב הבית | סדר | ארגון‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/karin.handyt/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏קרין קקון - הנדית - יוצרת תוכן - </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/the_home_land/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏שָׁנִיר חן - עיצוב הבית | סדר וארגון </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ohad.the.nomad</t>
+  </si>
+  <si>
+    <t>אוהד הנווד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/uri_liron/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אורי לירון | נווד במשרה מלאה </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/arielron12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אריאל רון‏ מטייל טרמפים ועוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mayalisker/</t>
+  </si>
+  <si>
+    <t>בחורה בעלת סוכנות נסיעות והתמכרות לטיסות‏‎✈️</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/you.like.travel/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חובב משאות - אנגלית </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hen.yoseff/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎חן יוסף טיולים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/flying.tali/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎טלי כהן טיילנית </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/liav.bohbot/</t>
+  </si>
+  <si>
+    <t>‏‎עוזר לכם לטייל🌏 יוצר תוכן בחור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ilay.stoller/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏קומיקאי אילי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/nevo.amrani/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> כוכב מצחיק - ילד ישראלי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/donev1_/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎דויד דונב, סרטוני הומור, </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/jonathan.keren/</t>
+  </si>
+  <si>
+    <t>יונתן קרן בדרן ישראל</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/elai_shamsian23/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏שמסי‏ קומיקאי </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/arad_shemi/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎ארד שמי הומור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dvir33/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎דביר איילת-השחר הומור ועוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shalevbagrish/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎שלו בגריש הומור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asaf.gothelf/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">אסף גוטלף בחור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itamarerenberg/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎איתמר ארנברג </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dvir.turjman/?g=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏דביר תורג'מן‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yuvaliron/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יובל בדיחות אבא ברחוב </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ben_avraham_10/</t>
+  </si>
+  <si>
+    <t>בן אברן משחקי חברה</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/stavasraf91/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎סתיו אסרף הומור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dudi_friedman/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">דודי פרדימן חסיד מעריץ זמרים </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakov__azulay/</t>
+  </si>
+  <si>
+    <t>יעקב אזולאי - אורגניסט חרדי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/djamirambl/</t>
+  </si>
+  <si>
+    <t>עמירם בן לולו</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meni_hollender/</t>
+  </si>
+  <si>
+    <t>מני הולנדר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asher_grayber/</t>
+  </si>
+  <si>
+    <t>אשר גרייבר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mhasidim/</t>
+  </si>
+  <si>
+    <t>מרדכי חסידים</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israelbograd2/</t>
+  </si>
+  <si>
+    <t>ישראל בוגרד</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/israel_cohen_news/</t>
+  </si>
+  <si>
+    <t>ישראל כהן חרדי איש תקשורת</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/meny_shifman22/</t>
+  </si>
+  <si>
+    <t>מני שיפמן ביתר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/motizalmanov/</t>
+  </si>
+  <si>
+    <t>מוטי זלמנוב כוכב חרדי</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yesi.dya/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏ידידיה אפשטיין 💥💫חשבון אישי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haravmargalit/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב יהושע מרגלית - העמוד הרשמי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/efiskako/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אפי סקקובסקי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avidror9/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎אבי דרור </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yochanan_uri/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏יוחנן אורי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/aviel_uda/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אביאל עודה דוגמן </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/avinoam.d/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏אבינועם דריקס </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/itzik_ohana_/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏איציק אוחנה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ze_lama/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מלך זילבר שלג </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/yakireisner/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎יעקי רייסנר וורט </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shiner_music/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎שיינר מפיק דתי של איתי דוד </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/benytoker2/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏בני טוקר‏ עיתונאי דתי  </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shlomigil/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏שלומי גיל‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mendiroth/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏מענדל ראטה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/asdfg_hjk3179/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הערשי אייזנשטיין‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shmuel.akerman/</t>
+  </si>
+  <si>
+    <t>שמואל אקרמן דתי | שיווק וסרטונים לזמרים | הפקות קאברים | זמר ויוצר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/menachem.toker/</t>
+  </si>
+  <si>
+    <t>מנחם טוקר</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dudikepler/</t>
+  </si>
+  <si>
+    <t>דודי קפלר הפרופסור</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/david_gurwitz/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏‎דוד גורביץ דתי אבא </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/david_dbx1/</t>
+  </si>
+  <si>
+    <t>דודו בניאק בחור דתי מבני ברק מעריץ של שרק</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/shimi_boki/</t>
+  </si>
+  <si>
+    <t>‎שימי בקשפן בחור חסיד‎ (@shimi_boki) • Instagram photos and videos</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haravigalcohen10/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב יגאל כהן‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haravigalcohen_shiorim/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב יגאל כהן-רשמי‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/haravfanger/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב יצחק פנגר‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/rav_shalom__arush/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‏הרב שלום ארוש- גן האמונה‏ </t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lionelrobine/</t>
+  </si>
+  <si>
+    <t>ליונלרובין יוצר תוכן לזיכוי הרבים</t>
   </si>
 </sst>
 </file>
@@ -929,11 +3791,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314C898-9C37-4B5F-A425-225D45F41FA8}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B495"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="31.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -945,18 +3807,3890 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>112</v>
+      </c>
+      <c r="B63" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>114</v>
+      </c>
+      <c r="B65" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>115</v>
+      </c>
+      <c r="B66" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>116</v>
+      </c>
+      <c r="B67" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>117</v>
+      </c>
+      <c r="B68" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>118</v>
+      </c>
+      <c r="B69" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>120</v>
+      </c>
+      <c r="B72" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>121</v>
+      </c>
+      <c r="B73" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>122</v>
+      </c>
+      <c r="B74" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>123</v>
+      </c>
+      <c r="B75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>124</v>
+      </c>
+      <c r="B76" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>125</v>
+      </c>
+      <c r="B77" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>127</v>
+      </c>
+      <c r="B79" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>128</v>
+      </c>
+      <c r="B80" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>129</v>
+      </c>
+      <c r="B81" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>130</v>
+      </c>
+      <c r="B82" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>131</v>
+      </c>
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>132</v>
+      </c>
+      <c r="B84" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>133</v>
+      </c>
+      <c r="B85" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>134</v>
+      </c>
+      <c r="B86" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>114</v>
+      </c>
+      <c r="B87" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>135</v>
+      </c>
+      <c r="B89" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>136</v>
+      </c>
+      <c r="B90" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>137</v>
+      </c>
+      <c r="B92" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>138</v>
+      </c>
+      <c r="B93" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>139</v>
+      </c>
+      <c r="B94" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>177</v>
+      </c>
+      <c r="B98" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>179</v>
+      </c>
+      <c r="B99" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>183</v>
+      </c>
+      <c r="B101" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>185</v>
+      </c>
+      <c r="B102" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>189</v>
+      </c>
+      <c r="B104" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>191</v>
+      </c>
+      <c r="B105" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>193</v>
+      </c>
+      <c r="B106" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>195</v>
+      </c>
+      <c r="B107" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>197</v>
+      </c>
+      <c r="B108" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>199</v>
+      </c>
+      <c r="B109" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>201</v>
+      </c>
+      <c r="B110" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>203</v>
+      </c>
+      <c r="B111" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>205</v>
+      </c>
+      <c r="B112" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>207</v>
+      </c>
+      <c r="B113" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>209</v>
+      </c>
+      <c r="B114" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>211</v>
+      </c>
+      <c r="B115" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>213</v>
+      </c>
+      <c r="B116" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>215</v>
+      </c>
+      <c r="B117" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>217</v>
+      </c>
+      <c r="B118" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>219</v>
+      </c>
+      <c r="B119" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>221</v>
+      </c>
+      <c r="B120" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>223</v>
+      </c>
+      <c r="B121" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>225</v>
+      </c>
+      <c r="B122" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>227</v>
+      </c>
+      <c r="B123" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>229</v>
+      </c>
+      <c r="B124" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>231</v>
+      </c>
+      <c r="B125" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>233</v>
+      </c>
+      <c r="B126" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>235</v>
+      </c>
+      <c r="B127" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>237</v>
+      </c>
+      <c r="B128" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>239</v>
+      </c>
+      <c r="B129" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>241</v>
+      </c>
+      <c r="B130" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>243</v>
+      </c>
+      <c r="B131" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>245</v>
+      </c>
+      <c r="B132" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>247</v>
+      </c>
+      <c r="B133" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>249</v>
+      </c>
+      <c r="B134" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>251</v>
+      </c>
+      <c r="B135" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>253</v>
+      </c>
+      <c r="B136" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>255</v>
+      </c>
+      <c r="B137" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>257</v>
+      </c>
+      <c r="B138" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>259</v>
+      </c>
+      <c r="B139" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>261</v>
+      </c>
+      <c r="B140" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>263</v>
+      </c>
+      <c r="B141" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>265</v>
+      </c>
+      <c r="B142" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>267</v>
+      </c>
+      <c r="B143" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>269</v>
+      </c>
+      <c r="B144" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>271</v>
+      </c>
+      <c r="B145" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>273</v>
+      </c>
+      <c r="B146" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>275</v>
+      </c>
+      <c r="B147" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>277</v>
+      </c>
+      <c r="B148" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>279</v>
+      </c>
+      <c r="B149" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>281</v>
+      </c>
+      <c r="B150" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>283</v>
+      </c>
+      <c r="B151" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>285</v>
+      </c>
+      <c r="B152" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>287</v>
+      </c>
+      <c r="B153" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>289</v>
+      </c>
+      <c r="B154" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>291</v>
+      </c>
+      <c r="B155" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>293</v>
+      </c>
+      <c r="B156" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>295</v>
+      </c>
+      <c r="B157" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>297</v>
+      </c>
+      <c r="B158" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>299</v>
+      </c>
+      <c r="B159" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>301</v>
+      </c>
+      <c r="B160" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>303</v>
+      </c>
+      <c r="B161" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>305</v>
+      </c>
+      <c r="B162" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>307</v>
+      </c>
+      <c r="B163" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>309</v>
+      </c>
+      <c r="B164" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>311</v>
+      </c>
+      <c r="B165" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>305</v>
+      </c>
+      <c r="B166" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>314</v>
+      </c>
+      <c r="B167" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>316</v>
+      </c>
+      <c r="B168" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>318</v>
+      </c>
+      <c r="B169" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>320</v>
+      </c>
+      <c r="B170" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>322</v>
+      </c>
+      <c r="B171" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>324</v>
+      </c>
+      <c r="B172" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>326</v>
+      </c>
+      <c r="B173" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>328</v>
+      </c>
+      <c r="B174" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>330</v>
+      </c>
+      <c r="B175" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>332</v>
+      </c>
+      <c r="B176" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>334</v>
+      </c>
+      <c r="B177" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>336</v>
+      </c>
+      <c r="B178" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>338</v>
+      </c>
+      <c r="B179" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>340</v>
+      </c>
+      <c r="B180" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>342</v>
+      </c>
+      <c r="B181" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>344</v>
+      </c>
+      <c r="B182" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>346</v>
+      </c>
+      <c r="B183" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>348</v>
+      </c>
+      <c r="B184" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>350</v>
+      </c>
+      <c r="B185" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>351</v>
+      </c>
+      <c r="B187" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>353</v>
+      </c>
+      <c r="B188" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>355</v>
+      </c>
+      <c r="B189" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>357</v>
+      </c>
+      <c r="B190" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>359</v>
+      </c>
+      <c r="B191" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>361</v>
+      </c>
+      <c r="B192" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>363</v>
+      </c>
+      <c r="B193" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>365</v>
+      </c>
+      <c r="B194" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>367</v>
+      </c>
+      <c r="B195" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>369</v>
+      </c>
+      <c r="B196" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>371</v>
+      </c>
+      <c r="B197" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>373</v>
+      </c>
+      <c r="B198" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>375</v>
+      </c>
+      <c r="B199" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>377</v>
+      </c>
+      <c r="B200" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>379</v>
+      </c>
+      <c r="B201" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>381</v>
+      </c>
+      <c r="B202" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>383</v>
+      </c>
+      <c r="B203" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>385</v>
+      </c>
+      <c r="B204" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>387</v>
+      </c>
+      <c r="B205" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>389</v>
+      </c>
+      <c r="B206" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>391</v>
+      </c>
+      <c r="B207" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>393</v>
+      </c>
+      <c r="B208" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>395</v>
+      </c>
+      <c r="B209" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>397</v>
+      </c>
+      <c r="B210" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>399</v>
+      </c>
+      <c r="B211" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>401</v>
+      </c>
+      <c r="B212" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>403</v>
+      </c>
+      <c r="B213" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>405</v>
+      </c>
+      <c r="B214" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>407</v>
+      </c>
+      <c r="B215" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>409</v>
+      </c>
+      <c r="B217" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>411</v>
+      </c>
+      <c r="B218" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>413</v>
+      </c>
+      <c r="B219" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>415</v>
+      </c>
+      <c r="B220" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>417</v>
+      </c>
+      <c r="B221" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>419</v>
+      </c>
+      <c r="B222" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>421</v>
+      </c>
+      <c r="B223" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>423</v>
+      </c>
+      <c r="B224" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>425</v>
+      </c>
+      <c r="B225" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>427</v>
+      </c>
+      <c r="B226" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>429</v>
+      </c>
+      <c r="B227" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>431</v>
+      </c>
+      <c r="B228" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>433</v>
+      </c>
+      <c r="B229" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>435</v>
+      </c>
+      <c r="B230" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>437</v>
+      </c>
+      <c r="B231" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>439</v>
+      </c>
+      <c r="B232" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>441</v>
+      </c>
+      <c r="B233" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>443</v>
+      </c>
+      <c r="B234" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>445</v>
+      </c>
+      <c r="B235" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>447</v>
+      </c>
+      <c r="B236" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>449</v>
+      </c>
+      <c r="B237" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>450</v>
+      </c>
+      <c r="B238" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>452</v>
+      </c>
+      <c r="B239" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>454</v>
+      </c>
+      <c r="B240" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>456</v>
+      </c>
+      <c r="B241" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>458</v>
+      </c>
+      <c r="B242" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>460</v>
+      </c>
+      <c r="B243" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>462</v>
+      </c>
+      <c r="B244" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>464</v>
+      </c>
+      <c r="B245" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>466</v>
+      </c>
+      <c r="B246" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>468</v>
+      </c>
+      <c r="B247" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>470</v>
+      </c>
+      <c r="B248" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>472</v>
+      </c>
+      <c r="B249" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>474</v>
+      </c>
+      <c r="B250" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>476</v>
+      </c>
+      <c r="B251" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>478</v>
+      </c>
+      <c r="B252" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>480</v>
+      </c>
+      <c r="B253" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>482</v>
+      </c>
+      <c r="B254" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>484</v>
+      </c>
+      <c r="B255" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>486</v>
+      </c>
+      <c r="B256" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>488</v>
+      </c>
+      <c r="B257" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>490</v>
+      </c>
+      <c r="B258" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>492</v>
+      </c>
+      <c r="B259" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>494</v>
+      </c>
+      <c r="B260" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>496</v>
+      </c>
+      <c r="B261" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>498</v>
+      </c>
+      <c r="B262" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>500</v>
+      </c>
+      <c r="B263" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>502</v>
+      </c>
+      <c r="B264" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>504</v>
+      </c>
+      <c r="B265" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>506</v>
+      </c>
+      <c r="B266" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>508</v>
+      </c>
+      <c r="B267" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>510</v>
+      </c>
+      <c r="B268" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>512</v>
+      </c>
+      <c r="B269" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>514</v>
+      </c>
+      <c r="B270" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>516</v>
+      </c>
+      <c r="B271" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>518</v>
+      </c>
+      <c r="B272" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>520</v>
+      </c>
+      <c r="B273" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>522</v>
+      </c>
+      <c r="B274" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>524</v>
+      </c>
+      <c r="B275" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>526</v>
+      </c>
+      <c r="B276" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>528</v>
+      </c>
+      <c r="B277" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>530</v>
+      </c>
+      <c r="B278" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>532</v>
+      </c>
+      <c r="B279" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>534</v>
+      </c>
+      <c r="B280" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>536</v>
+      </c>
+      <c r="B281" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>538</v>
+      </c>
+      <c r="B282" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>540</v>
+      </c>
+      <c r="B283" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>542</v>
+      </c>
+      <c r="B284" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>544</v>
+      </c>
+      <c r="B285" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>546</v>
+      </c>
+      <c r="B286" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>548</v>
+      </c>
+      <c r="B287" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>550</v>
+      </c>
+      <c r="B288" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>552</v>
+      </c>
+      <c r="B289" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>554</v>
+      </c>
+      <c r="B290" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>556</v>
+      </c>
+      <c r="B291" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>558</v>
+      </c>
+      <c r="B292" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>560</v>
+      </c>
+      <c r="B293" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>562</v>
+      </c>
+      <c r="B294" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>564</v>
+      </c>
+      <c r="B295" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>215</v>
+      </c>
+      <c r="B296" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>567</v>
+      </c>
+      <c r="B297" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>569</v>
+      </c>
+      <c r="B298" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>571</v>
+      </c>
+      <c r="B299" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>573</v>
+      </c>
+      <c r="B300" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>575</v>
+      </c>
+      <c r="B301" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>577</v>
+      </c>
+      <c r="B302" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>579</v>
+      </c>
+      <c r="B303" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>581</v>
+      </c>
+      <c r="B304" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>583</v>
+      </c>
+      <c r="B305" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>585</v>
+      </c>
+      <c r="B306" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>587</v>
+      </c>
+      <c r="B307" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>589</v>
+      </c>
+      <c r="B308" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>591</v>
+      </c>
+      <c r="B309" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>593</v>
+      </c>
+      <c r="B310" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>595</v>
+      </c>
+      <c r="B311" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>597</v>
+      </c>
+      <c r="B312" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" t="s">
+        <v>599</v>
+      </c>
+      <c r="B313" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" t="s">
+        <v>601</v>
+      </c>
+      <c r="B314" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" t="s">
+        <v>603</v>
+      </c>
+      <c r="B315" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" t="s">
+        <v>605</v>
+      </c>
+      <c r="B316" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" t="s">
+        <v>607</v>
+      </c>
+      <c r="B317" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" t="s">
+        <v>609</v>
+      </c>
+      <c r="B318" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" t="s">
+        <v>611</v>
+      </c>
+      <c r="B319" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
+        <v>613</v>
+      </c>
+      <c r="B320" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321" t="s">
+        <v>615</v>
+      </c>
+      <c r="B321" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322" t="s">
+        <v>617</v>
+      </c>
+      <c r="B322" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323" t="s">
+        <v>619</v>
+      </c>
+      <c r="B323" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324" t="s">
+        <v>621</v>
+      </c>
+      <c r="B324" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325" t="s">
+        <v>623</v>
+      </c>
+      <c r="B325" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326" t="s">
+        <v>625</v>
+      </c>
+      <c r="B326" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327" t="s">
+        <v>627</v>
+      </c>
+      <c r="B327" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A328" t="s">
+        <v>629</v>
+      </c>
+      <c r="B328" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A329" t="s">
+        <v>631</v>
+      </c>
+      <c r="B329" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A330" t="s">
+        <v>633</v>
+      </c>
+      <c r="B330" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A331" t="s">
+        <v>635</v>
+      </c>
+      <c r="B331" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>637</v>
+      </c>
+      <c r="B332" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A333" t="s">
+        <v>639</v>
+      </c>
+      <c r="B333" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A334" t="s">
+        <v>641</v>
+      </c>
+      <c r="B334" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A335" t="s">
+        <v>643</v>
+      </c>
+      <c r="B335" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A336" t="s">
+        <v>645</v>
+      </c>
+      <c r="B336" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>647</v>
+      </c>
+      <c r="B337" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>649</v>
+      </c>
+      <c r="B338" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>651</v>
+      </c>
+      <c r="B339" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>653</v>
+      </c>
+      <c r="B340" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>655</v>
+      </c>
+      <c r="B341" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>657</v>
+      </c>
+      <c r="B342" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>659</v>
+      </c>
+      <c r="B343" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>661</v>
+      </c>
+      <c r="B344" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A345" t="s">
+        <v>663</v>
+      </c>
+      <c r="B345" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A346" t="s">
+        <v>665</v>
+      </c>
+      <c r="B346" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A347" t="s">
+        <v>667</v>
+      </c>
+      <c r="B347" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A349" t="s">
+        <v>669</v>
+      </c>
+      <c r="B349" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>671</v>
+      </c>
+      <c r="B350" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>673</v>
+      </c>
+      <c r="B351" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
+        <v>675</v>
+      </c>
+      <c r="B352" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A353" t="s">
+        <v>677</v>
+      </c>
+      <c r="B353" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
+        <v>679</v>
+      </c>
+      <c r="B354" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
+        <v>681</v>
+      </c>
+      <c r="B355" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356" t="s">
+        <v>683</v>
+      </c>
+      <c r="B356" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357" t="s">
+        <v>685</v>
+      </c>
+      <c r="B357" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A358" t="s">
+        <v>687</v>
+      </c>
+      <c r="B358" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359" t="s">
+        <v>689</v>
+      </c>
+      <c r="B359" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A360" t="s">
+        <v>691</v>
+      </c>
+      <c r="B360" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A361" t="s">
+        <v>693</v>
+      </c>
+      <c r="B361" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A362" t="s">
+        <v>695</v>
+      </c>
+      <c r="B362" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A363" t="s">
+        <v>697</v>
+      </c>
+      <c r="B363" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
+        <v>699</v>
+      </c>
+      <c r="B364" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365" t="s">
+        <v>675</v>
+      </c>
+      <c r="B365" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366" t="s">
+        <v>702</v>
+      </c>
+      <c r="B366" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
+        <v>704</v>
+      </c>
+      <c r="B367" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
+        <v>706</v>
+      </c>
+      <c r="B368" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369" t="s">
+        <v>708</v>
+      </c>
+      <c r="B369" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370" t="s">
+        <v>710</v>
+      </c>
+      <c r="B370" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371" t="s">
+        <v>712</v>
+      </c>
+      <c r="B371" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372" t="s">
+        <v>714</v>
+      </c>
+      <c r="B372" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374" t="s">
+        <v>716</v>
+      </c>
+      <c r="B374" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375" t="s">
+        <v>718</v>
+      </c>
+      <c r="B375" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376" t="s">
+        <v>720</v>
+      </c>
+      <c r="B376" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377" t="s">
+        <v>722</v>
+      </c>
+      <c r="B377" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
+        <v>724</v>
+      </c>
+      <c r="B378" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>726</v>
+      </c>
+      <c r="B379" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>728</v>
+      </c>
+      <c r="B380" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>730</v>
+      </c>
+      <c r="B381" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>732</v>
+      </c>
+      <c r="B382" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>734</v>
+      </c>
+      <c r="B383" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>736</v>
+      </c>
+      <c r="B384" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>738</v>
+      </c>
+      <c r="B385" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>740</v>
+      </c>
+      <c r="B386" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>742</v>
+      </c>
+      <c r="B387" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>744</v>
+      </c>
+      <c r="B388" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>746</v>
+      </c>
+      <c r="B389" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>748</v>
+      </c>
+      <c r="B390" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>750</v>
+      </c>
+      <c r="B391" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>752</v>
+      </c>
+      <c r="B392" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>754</v>
+      </c>
+      <c r="B393" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>756</v>
+      </c>
+      <c r="B394" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>758</v>
+      </c>
+      <c r="B395" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A396" t="s">
+        <v>760</v>
+      </c>
+      <c r="B396" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A397" t="s">
+        <v>762</v>
+      </c>
+      <c r="B397" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A398" t="s">
+        <v>764</v>
+      </c>
+      <c r="B398" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A399" t="s">
+        <v>766</v>
+      </c>
+      <c r="B399" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>768</v>
+      </c>
+      <c r="B400" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A401" t="s">
+        <v>770</v>
+      </c>
+      <c r="B401" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A402" t="s">
+        <v>772</v>
+      </c>
+      <c r="B402" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403" t="s">
+        <v>774</v>
+      </c>
+      <c r="B403" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>776</v>
+      </c>
+      <c r="B404" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A405" t="s">
+        <v>778</v>
+      </c>
+      <c r="B405" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A406" t="s">
+        <v>780</v>
+      </c>
+      <c r="B406" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>782</v>
+      </c>
+      <c r="B407" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>784</v>
+      </c>
+      <c r="B408" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A409" t="s">
+        <v>786</v>
+      </c>
+      <c r="B409" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A410" t="s">
+        <v>788</v>
+      </c>
+      <c r="B410" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
+        <v>790</v>
+      </c>
+      <c r="B411" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A412" t="s">
+        <v>792</v>
+      </c>
+      <c r="B412" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A413" t="s">
+        <v>794</v>
+      </c>
+      <c r="B413" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A414" t="s">
+        <v>796</v>
+      </c>
+      <c r="B414" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A415" t="s">
+        <v>798</v>
+      </c>
+      <c r="B415" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A416" t="s">
+        <v>800</v>
+      </c>
+      <c r="B416" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>802</v>
+      </c>
+      <c r="B417" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A418" t="s">
+        <v>804</v>
+      </c>
+      <c r="B418" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A419" t="s">
+        <v>806</v>
+      </c>
+      <c r="B419" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A420" t="s">
+        <v>808</v>
+      </c>
+      <c r="B420" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A421" t="s">
+        <v>810</v>
+      </c>
+      <c r="B421" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A422" t="s">
+        <v>810</v>
+      </c>
+      <c r="B422" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A423" t="s">
+        <v>812</v>
+      </c>
+      <c r="B423" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
+        <v>814</v>
+      </c>
+      <c r="B424" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
+        <v>816</v>
+      </c>
+      <c r="B425" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
+        <v>818</v>
+      </c>
+      <c r="B426" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
+        <v>820</v>
+      </c>
+      <c r="B427" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
+        <v>822</v>
+      </c>
+      <c r="B428" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A429" t="s">
+        <v>824</v>
+      </c>
+      <c r="B429" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>826</v>
+      </c>
+      <c r="B430" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>828</v>
+      </c>
+      <c r="B431" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
+        <v>830</v>
+      </c>
+      <c r="B432" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>832</v>
+      </c>
+      <c r="B433" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>834</v>
+      </c>
+      <c r="B434" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>836</v>
+      </c>
+      <c r="B435" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>838</v>
+      </c>
+      <c r="B436" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
+        <v>840</v>
+      </c>
+      <c r="B437" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A438" t="s">
+        <v>842</v>
+      </c>
+      <c r="B438" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A439" t="s">
+        <v>844</v>
+      </c>
+      <c r="B439" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>846</v>
+      </c>
+      <c r="B440" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A441" t="s">
+        <v>848</v>
+      </c>
+      <c r="B441" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A442" t="s">
+        <v>850</v>
+      </c>
+      <c r="B442" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A443" t="s">
+        <v>852</v>
+      </c>
+      <c r="B443" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A444" t="s">
+        <v>854</v>
+      </c>
+      <c r="B444" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A445" t="s">
+        <v>856</v>
+      </c>
+      <c r="B445" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A446" t="s">
+        <v>858</v>
+      </c>
+      <c r="B446" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A447" t="s">
+        <v>860</v>
+      </c>
+      <c r="B447" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>862</v>
+      </c>
+      <c r="B448" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>864</v>
+      </c>
+      <c r="B449" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>866</v>
+      </c>
+      <c r="B450" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>868</v>
+      </c>
+      <c r="B451" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>870</v>
+      </c>
+      <c r="B452" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>872</v>
+      </c>
+      <c r="B453" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>874</v>
+      </c>
+      <c r="B454" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>876</v>
+      </c>
+      <c r="B455" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>878</v>
+      </c>
+      <c r="B456" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>880</v>
+      </c>
+      <c r="B457" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>882</v>
+      </c>
+      <c r="B458" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>884</v>
+      </c>
+      <c r="B459" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>261</v>
+      </c>
+      <c r="B460" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>886</v>
+      </c>
+      <c r="B461" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>888</v>
+      </c>
+      <c r="B462" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>890</v>
+      </c>
+      <c r="B463" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>892</v>
+      </c>
+      <c r="B464" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>894</v>
+      </c>
+      <c r="B465" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>896</v>
+      </c>
+      <c r="B466" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>898</v>
+      </c>
+      <c r="B467" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>900</v>
+      </c>
+      <c r="B468" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>902</v>
+      </c>
+      <c r="B469" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>904</v>
+      </c>
+      <c r="B470" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>906</v>
+      </c>
+      <c r="B471" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>908</v>
+      </c>
+      <c r="B472" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>910</v>
+      </c>
+      <c r="B473" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>912</v>
+      </c>
+      <c r="B474" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A475" t="s">
+        <v>914</v>
+      </c>
+      <c r="B475" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A476" t="s">
+        <v>916</v>
+      </c>
+      <c r="B476" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A477" t="s">
+        <v>918</v>
+      </c>
+      <c r="B477" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A478" t="s">
+        <v>920</v>
+      </c>
+      <c r="B478" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A479" t="s">
+        <v>922</v>
+      </c>
+      <c r="B479" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A480" t="s">
+        <v>924</v>
+      </c>
+      <c r="B480" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>926</v>
+      </c>
+      <c r="B481" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>928</v>
+      </c>
+      <c r="B482" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>930</v>
+      </c>
+      <c r="B483" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>932</v>
+      </c>
+      <c r="B484" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>934</v>
+      </c>
+      <c r="B485" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>936</v>
+      </c>
+      <c r="B486" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A487" t="s">
+        <v>938</v>
+      </c>
+      <c r="B487" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A488" t="s">
+        <v>940</v>
+      </c>
+      <c r="B488" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>942</v>
+      </c>
+      <c r="B489" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A490" t="s">
+        <v>944</v>
+      </c>
+      <c r="B490" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A491" t="s">
+        <v>946</v>
+      </c>
+      <c r="B491" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A492" t="s">
+        <v>948</v>
+      </c>
+      <c r="B492" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A493" t="s">
+        <v>950</v>
+      </c>
+      <c r="B493" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A494" t="s">
+        <v>952</v>
+      </c>
+      <c r="B494" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A495" t="s">
+        <v>954</v>
+      </c>
+      <c r="B495" t="s">
+        <v>955</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{B2FECCC5-FAF8-407D-8016-358AD744B92A}"/>
+    <hyperlink ref="A14" r:id="rId2" xr:uid="{A671A1D5-E943-4EA2-9220-0055F332FE00}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>